--- a/cuadros/ABRIL/Abril_SantaRita_Mora.xlsx
+++ b/cuadros/ABRIL/Abril_SantaRita_Mora.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MONITOR7\Desktop\Fiscalizaciones viejas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\FISCALIZACION\cuadros\ABRIL\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA831B5E-E999-43B7-84F1-3B1817EE75F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12800" windowHeight="4893"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +19,19 @@
   <externalReferences>
     <externalReference r:id="rId3"/>
   </externalReferences>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -349,7 +362,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="000000"/>
   </numFmts>
@@ -386,7 +399,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -408,12 +421,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -537,9 +544,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -575,6 +579,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -607,7 +614,7 @@
         <xdr:cNvPr id="2" name="CuadroTexto 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5C6DCA20-975D-426A-B5AE-98554BBAD33C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -662,7 +669,7 @@
         <xdr:cNvPr id="3" name="CuadroTexto 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{35F97302-5243-4622-A8AE-8654558AE536}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -717,7 +724,7 @@
         <xdr:cNvPr id="4" name="CuadroTexto 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{971E24A2-06B5-4991-B0A3-8CBAFBC3EE08}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -772,7 +779,7 @@
         <xdr:cNvPr id="5" name="CuadroTexto 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4D6564E3-B14D-46A1-B81F-69CCF7111617}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -827,7 +834,7 @@
         <xdr:cNvPr id="6" name="CuadroTexto 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{87D93D75-9DDD-47C1-BBE3-98B16379633E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -882,7 +889,7 @@
         <xdr:cNvPr id="7" name="CuadroTexto 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E22C7FD0-7AAD-4EAD-A0FC-DAFB34392E25}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -937,7 +944,7 @@
         <xdr:cNvPr id="8" name="CuadroTexto 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D225C2B8-1EDD-40D7-9C3C-741523E9E822}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -992,7 +999,7 @@
         <xdr:cNvPr id="9" name="CuadroTexto 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{ECC5E016-833E-47AF-BDA1-C693C795E1FD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1047,7 +1054,7 @@
         <xdr:cNvPr id="10" name="CuadroTexto 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A75C6DE4-57F1-4925-907B-5D08A05ACAA6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1102,7 +1109,7 @@
         <xdr:cNvPr id="11" name="CuadroTexto 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4E661821-E41D-409E-A479-1B1EDEE26329}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1157,7 +1164,7 @@
         <xdr:cNvPr id="12" name="CuadroTexto 11">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6EF617BF-FA51-4493-BD85-407E4691D777}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1212,7 +1219,7 @@
         <xdr:cNvPr id="13" name="CuadroTexto 12">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C69510D8-31CD-4D62-9B5F-0B3C65DBD694}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1267,7 +1274,7 @@
         <xdr:cNvPr id="14" name="CuadroTexto 13">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E25F6EE1-DB29-472A-911B-425BDAE8F999}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1322,7 +1329,7 @@
         <xdr:cNvPr id="15" name="CuadroTexto 14">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9B75DCA7-709D-4185-BA61-FF14BE352E64}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1377,7 +1384,7 @@
         <xdr:cNvPr id="16" name="CuadroTexto 15">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6ED5C0E6-2818-48E4-91D1-FE29F079AFA6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000010000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1432,7 +1439,7 @@
         <xdr:cNvPr id="17" name="CuadroTexto 16">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2C8E96A3-17CB-4B71-86BB-E36B4F02E426}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000011000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1487,7 +1494,7 @@
         <xdr:cNvPr id="18" name="CuadroTexto 17">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D27999A5-27D7-4D7A-9482-4457AC72810D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000012000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1542,7 +1549,7 @@
         <xdr:cNvPr id="19" name="CuadroTexto 18">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{63EB681C-77E3-40BC-84F3-63CBD3DF2F86}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000013000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1597,7 +1604,7 @@
         <xdr:cNvPr id="20" name="CuadroTexto 19">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0A48F321-6B96-47D0-A838-CB5DB8C655E8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000014000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1652,7 +1659,7 @@
         <xdr:cNvPr id="21" name="CuadroTexto 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A0C51D34-3A7F-4FB6-9B6D-769D69362442}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000015000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1707,7 +1714,7 @@
         <xdr:cNvPr id="22" name="CuadroTexto 21">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8E4C4518-FB84-46F8-BEAA-57DF0BAB6F59}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000016000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1762,7 +1769,7 @@
         <xdr:cNvPr id="23" name="CuadroTexto 22">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{DCC66F88-76CD-4D40-83F1-40876A4B75EC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000017000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1817,7 +1824,7 @@
         <xdr:cNvPr id="24" name="CuadroTexto 23">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2FA5E455-4F77-4FD5-B8C1-8D79C3285A2E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000018000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1872,7 +1879,7 @@
         <xdr:cNvPr id="25" name="CuadroTexto 24">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{27D86713-7948-42F7-8B6F-D9A8009B6960}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000019000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1927,7 +1934,7 @@
         <xdr:cNvPr id="26" name="CuadroTexto 25">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6C9DB0F2-D7AA-4405-9DBA-8E26F40247C5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1982,7 +1989,7 @@
         <xdr:cNvPr id="27" name="CuadroTexto 26">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A8EE627A-17D0-4E29-8820-F4227DE17601}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2037,7 +2044,7 @@
         <xdr:cNvPr id="28" name="CuadroTexto 27">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9457EBD3-2A52-40A9-BF33-47E1D5E6B881}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2092,7 +2099,7 @@
         <xdr:cNvPr id="29" name="CuadroTexto 28">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{76E168C6-F378-47FF-8527-40CEF96B33D7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2147,7 +2154,7 @@
         <xdr:cNvPr id="30" name="CuadroTexto 29">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9E0C8249-4399-4BA2-BA5C-D7EB7F649410}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2202,7 +2209,7 @@
         <xdr:cNvPr id="31" name="CuadroTexto 30">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F844C091-2560-4301-BAF3-8068E0BAC55F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2257,7 +2264,7 @@
         <xdr:cNvPr id="32" name="CuadroTexto 31">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{35E230D2-65C6-4D3A-A509-7A30A1DD16A9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000020000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2312,7 +2319,7 @@
         <xdr:cNvPr id="33" name="CuadroTexto 32">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2EDBF8D8-7718-4726-A28C-81FA2ABDD45C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000021000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2367,7 +2374,7 @@
         <xdr:cNvPr id="34" name="CuadroTexto 33">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{38C14B10-6A0F-404A-82D7-47DC8C25A9CF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000022000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2422,7 +2429,7 @@
         <xdr:cNvPr id="35" name="CuadroTexto 34">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{68714B55-10B6-45CF-A3C1-0C0DAFC9FE2F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000023000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2477,7 +2484,7 @@
         <xdr:cNvPr id="36" name="CuadroTexto 35">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8CEFAF49-3ECC-48A2-AB1B-F4D575F95D93}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000024000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2532,7 +2539,7 @@
         <xdr:cNvPr id="37" name="CuadroTexto 36">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{1C11B0AF-A88B-425E-896C-38E47E95AE3C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000025000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2587,7 +2594,7 @@
         <xdr:cNvPr id="38" name="CuadroTexto 37">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9EB2576E-BAA9-442D-B03F-5E5B126476B2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000026000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2642,7 +2649,7 @@
         <xdr:cNvPr id="39" name="CuadroTexto 38">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C5ECD0FF-09D1-48E2-9B9E-3891CAAB79DF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000027000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2697,7 +2704,7 @@
         <xdr:cNvPr id="40" name="CuadroTexto 39">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A2655A27-C726-4427-8CDA-3F7CFB138A74}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000028000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2752,7 +2759,7 @@
         <xdr:cNvPr id="41" name="CuadroTexto 40">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A44DBF10-9E50-4594-B078-9E09C4F548CA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000029000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2807,7 +2814,7 @@
         <xdr:cNvPr id="42" name="CuadroTexto 41">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7139675D-98B0-457B-892F-D071C2122634}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2862,7 +2869,7 @@
         <xdr:cNvPr id="43" name="CuadroTexto 42">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{07CE8B83-2297-4638-9937-E9EFA75A1461}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2917,7 +2924,7 @@
         <xdr:cNvPr id="44" name="CuadroTexto 43">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2DE35652-3A7C-46D3-9CA6-8D8A23924C81}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2972,7 +2979,7 @@
         <xdr:cNvPr id="45" name="CuadroTexto 44">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E1413AD7-E126-425B-B490-4747CACA254F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3027,7 +3034,7 @@
         <xdr:cNvPr id="46" name="CuadroTexto 45">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A8905AAA-86DA-41DC-8662-D8DD27B102DE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3082,7 +3089,7 @@
         <xdr:cNvPr id="47" name="CuadroTexto 46">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{74E8CDEE-5046-49A2-9476-AE6AE13BE9B9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3137,7 +3144,7 @@
         <xdr:cNvPr id="48" name="CuadroTexto 47">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{B30B5C0F-6D57-4511-8AEE-E6F25F56C9DF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000030000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3192,7 +3199,7 @@
         <xdr:cNvPr id="49" name="CuadroTexto 48">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{B056B88E-0E38-4977-9A12-CEF45BB24762}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000031000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3247,7 +3254,7 @@
         <xdr:cNvPr id="50" name="CuadroTexto 49">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C62502B5-CA28-4665-ACEE-01BAE31B78DD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000032000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3302,7 +3309,7 @@
         <xdr:cNvPr id="51" name="CuadroTexto 50">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{AB323F71-0232-493A-9406-74959DB72B4A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000033000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3357,7 +3364,7 @@
         <xdr:cNvPr id="52" name="CuadroTexto 51">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{BA381632-1446-4A23-9D92-4D0728454AD7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000034000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3412,7 +3419,7 @@
         <xdr:cNvPr id="53" name="CuadroTexto 52">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{04931D77-294E-4693-95C7-CBEC805C7548}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000035000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3467,7 +3474,7 @@
         <xdr:cNvPr id="54" name="CuadroTexto 53">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6CDC3C0A-3091-41C6-A9E1-F6267C917B3A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000036000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3522,7 +3529,7 @@
         <xdr:cNvPr id="55" name="CuadroTexto 54">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5F5CA680-CAD2-4F39-8580-50453A230887}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000037000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3577,7 +3584,7 @@
         <xdr:cNvPr id="56" name="CuadroTexto 55">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4F31BCE1-E6DE-46F4-A930-6F5FB62D892A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000038000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3632,7 +3639,7 @@
         <xdr:cNvPr id="57" name="CuadroTexto 56">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{658CED27-26FC-4A1D-B6AC-9D726433C1F2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000039000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3687,7 +3694,7 @@
         <xdr:cNvPr id="58" name="CuadroTexto 57">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{EA8CC70B-8BD6-4442-B465-7E0DB9759CF4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3742,7 +3749,7 @@
         <xdr:cNvPr id="59" name="CuadroTexto 58">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0FAB82FB-B33D-496D-9C92-16657151B5B3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3797,7 +3804,7 @@
         <xdr:cNvPr id="60" name="CuadroTexto 59">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{969EEEFE-7928-4CEE-812D-8F79A8C4AFB7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3852,7 +3859,7 @@
         <xdr:cNvPr id="61" name="CuadroTexto 60">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8773DFFC-5EBA-4129-9396-58C5E3D0D6F1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3907,7 +3914,7 @@
         <xdr:cNvPr id="62" name="CuadroTexto 61">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7E0BCDA4-76CF-4653-9BD8-BB78D36A1B44}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3962,7 +3969,7 @@
         <xdr:cNvPr id="63" name="CuadroTexto 62">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{09D0F357-8BC0-426D-9C7F-36B33EA7EDB2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4017,7 +4024,7 @@
         <xdr:cNvPr id="64" name="CuadroTexto 63">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F5FA9D63-02F2-4083-AFEA-BC85CBB0BBF9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000040000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4072,7 +4079,7 @@
         <xdr:cNvPr id="65" name="CuadroTexto 64">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{1AC1FF37-2A96-4CA4-A4D3-9E1A67778BA3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000041000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4127,7 +4134,7 @@
         <xdr:cNvPr id="66" name="CuadroTexto 65">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D5E4C9FE-5389-4D27-8E73-8AF1C65D7DAF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000042000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4182,7 +4189,7 @@
         <xdr:cNvPr id="67" name="CuadroTexto 66">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A5DE5D70-BA42-4918-BFB8-322D1A83003D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000043000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4237,7 +4244,7 @@
         <xdr:cNvPr id="68" name="CuadroTexto 67">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{B1618B97-90B2-455C-9F5A-44BE21DCEC37}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4292,7 +4299,7 @@
         <xdr:cNvPr id="69" name="CuadroTexto 68">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4C0C4DE1-47C0-4F71-AB45-AF1CAEB85E58}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4347,7 +4354,7 @@
         <xdr:cNvPr id="70" name="CuadroTexto 69">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{52060FAA-DF77-48C2-9133-177B4658C899}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4402,7 +4409,7 @@
         <xdr:cNvPr id="71" name="CuadroTexto 70">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9E2C4242-91E4-4B93-854C-EED968965F83}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4457,7 +4464,7 @@
         <xdr:cNvPr id="72" name="CuadroTexto 71">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{299FC220-8A4C-49BE-8ED4-F18E0A39BBCA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4512,7 +4519,7 @@
         <xdr:cNvPr id="73" name="CuadroTexto 72">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{03B79463-C31E-4895-9F68-D895A5A30585}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4567,7 +4574,7 @@
         <xdr:cNvPr id="74" name="CuadroTexto 73">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6353DFA9-437C-4ECB-89B6-46D6602BD2DB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4622,7 +4629,7 @@
         <xdr:cNvPr id="75" name="CuadroTexto 74">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{70EE90A1-B2BD-49F9-AA5A-D37A49E13FDA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4677,7 +4684,7 @@
         <xdr:cNvPr id="76" name="CuadroTexto 75">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E71FAC61-1CC2-4ABA-BA98-C03F5DDFB6C4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4732,7 +4739,7 @@
         <xdr:cNvPr id="77" name="CuadroTexto 76">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{868531C5-7CFC-4BFD-9745-A30B2D199BB9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4787,7 +4794,7 @@
         <xdr:cNvPr id="78" name="CuadroTexto 77">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C9A975DC-E577-468E-B791-D92EA0A7C22C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4842,7 +4849,7 @@
         <xdr:cNvPr id="79" name="CuadroTexto 78">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E85028FC-C066-407A-A9CA-617CAACBD592}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4897,7 +4904,7 @@
         <xdr:cNvPr id="80" name="CuadroTexto 79">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D35DE71D-3A0C-4934-9A7F-8E95D268A3E6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4952,7 +4959,7 @@
         <xdr:cNvPr id="81" name="CuadroTexto 80">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5C6DCA20-975D-426A-B5AE-98554BBAD33C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5007,7 +5014,7 @@
         <xdr:cNvPr id="82" name="CuadroTexto 81">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{35F97302-5243-4622-A8AE-8654558AE536}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5062,7 +5069,7 @@
         <xdr:cNvPr id="83" name="CuadroTexto 82">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{971E24A2-06B5-4991-B0A3-8CBAFBC3EE08}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5117,7 +5124,7 @@
         <xdr:cNvPr id="84" name="CuadroTexto 83">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4D6564E3-B14D-46A1-B81F-69CCF7111617}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5172,7 +5179,7 @@
         <xdr:cNvPr id="85" name="CuadroTexto 84">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E25F6EE1-DB29-472A-911B-425BDAE8F999}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5227,7 +5234,7 @@
         <xdr:cNvPr id="86" name="CuadroTexto 85">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{DCC66F88-76CD-4D40-83F1-40876A4B75EC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5282,7 +5289,7 @@
         <xdr:cNvPr id="87" name="CuadroTexto 86">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2FA5E455-4F77-4FD5-B8C1-8D79C3285A2E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000057000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5337,7 +5344,7 @@
         <xdr:cNvPr id="88" name="CuadroTexto 87">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A75C6DE4-57F1-4925-907B-5D08A05ACAA6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5392,7 +5399,7 @@
         <xdr:cNvPr id="89" name="CuadroTexto 88">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9B75DCA7-709D-4185-BA61-FF14BE352E64}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5447,7 +5454,7 @@
         <xdr:cNvPr id="90" name="CuadroTexto 89">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{63EB681C-77E3-40BC-84F3-63CBD3DF2F86}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5502,7 +5509,7 @@
         <xdr:cNvPr id="91" name="CuadroTexto 90">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A0C51D34-3A7F-4FB6-9B6D-769D69362442}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5557,7 +5564,7 @@
         <xdr:cNvPr id="92" name="CuadroTexto 91">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8E4C4518-FB84-46F8-BEAA-57DF0BAB6F59}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5612,7 +5619,7 @@
         <xdr:cNvPr id="93" name="CuadroTexto 92">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6C9DB0F2-D7AA-4405-9DBA-8E26F40247C5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5667,7 +5674,7 @@
         <xdr:cNvPr id="94" name="CuadroTexto 93">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A8EE627A-17D0-4E29-8820-F4227DE17601}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5722,7 +5729,7 @@
         <xdr:cNvPr id="95" name="CuadroTexto 94">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9457EBD3-2A52-40A9-BF33-47E1D5E6B881}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5777,7 +5784,7 @@
         <xdr:cNvPr id="96" name="CuadroTexto 95">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{76E168C6-F378-47FF-8527-40CEF96B33D7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5832,7 +5839,7 @@
         <xdr:cNvPr id="97" name="CuadroTexto 96">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F844C091-2560-4301-BAF3-8068E0BAC55F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5887,7 +5894,7 @@
         <xdr:cNvPr id="98" name="CuadroTexto 97">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{35E230D2-65C6-4D3A-A509-7A30A1DD16A9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5942,7 +5949,7 @@
         <xdr:cNvPr id="99" name="CuadroTexto 98">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2EDBF8D8-7718-4726-A28C-81FA2ABDD45C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5997,7 +6004,7 @@
         <xdr:cNvPr id="100" name="CuadroTexto 99">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{68714B55-10B6-45CF-A3C1-0C0DAFC9FE2F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6052,7 +6059,7 @@
         <xdr:cNvPr id="101" name="CuadroTexto 100">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8CEFAF49-3ECC-48A2-AB1B-F4D575F95D93}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6107,7 +6114,7 @@
         <xdr:cNvPr id="102" name="CuadroTexto 101">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{1C11B0AF-A88B-425E-896C-38E47E95AE3C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000066000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6162,7 +6169,7 @@
         <xdr:cNvPr id="103" name="CuadroTexto 102">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C5ECD0FF-09D1-48E2-9B9E-3891CAAB79DF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6217,7 +6224,7 @@
         <xdr:cNvPr id="104" name="CuadroTexto 103">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A2655A27-C726-4427-8CDA-3F7CFB138A74}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6272,7 +6279,7 @@
         <xdr:cNvPr id="105" name="CuadroTexto 104">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A44DBF10-9E50-4594-B078-9E09C4F548CA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6327,7 +6334,7 @@
         <xdr:cNvPr id="106" name="CuadroTexto 105">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7139675D-98B0-457B-892F-D071C2122634}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6382,7 +6389,7 @@
         <xdr:cNvPr id="107" name="CuadroTexto 106">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2DE35652-3A7C-46D3-9CA6-8D8A23924C81}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6437,7 +6444,7 @@
         <xdr:cNvPr id="108" name="CuadroTexto 107">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0FAB82FB-B33D-496D-9C92-16657151B5B3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6492,7 +6499,7 @@
         <xdr:cNvPr id="109" name="CuadroTexto 108">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{969EEEFE-7928-4CEE-812D-8F79A8C4AFB7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6547,7 +6554,7 @@
         <xdr:cNvPr id="110" name="CuadroTexto 109">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8773DFFC-5EBA-4129-9396-58C5E3D0D6F1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6602,7 +6609,7 @@
         <xdr:cNvPr id="111" name="CuadroTexto 110">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7E0BCDA4-76CF-4653-9BD8-BB78D36A1B44}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6657,7 +6664,7 @@
         <xdr:cNvPr id="112" name="CuadroTexto 111">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{09D0F357-8BC0-426D-9C7F-36B33EA7EDB2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000070000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6712,7 +6719,7 @@
         <xdr:cNvPr id="113" name="CuadroTexto 112">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A75C6DE4-57F1-4925-907B-5D08A05ACAA6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000071000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6767,7 +6774,7 @@
         <xdr:cNvPr id="114" name="CuadroTexto 113">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9B75DCA7-709D-4185-BA61-FF14BE352E64}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000072000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6822,7 +6829,7 @@
         <xdr:cNvPr id="115" name="CuadroTexto 114">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{63EB681C-77E3-40BC-84F3-63CBD3DF2F86}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000073000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6877,7 +6884,7 @@
         <xdr:cNvPr id="116" name="CuadroTexto 115">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A0C51D34-3A7F-4FB6-9B6D-769D69362442}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000074000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6932,7 +6939,7 @@
         <xdr:cNvPr id="117" name="CuadroTexto 116">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8E4C4518-FB84-46F8-BEAA-57DF0BAB6F59}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000075000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6987,7 +6994,7 @@
         <xdr:cNvPr id="118" name="CuadroTexto 117">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6C9DB0F2-D7AA-4405-9DBA-8E26F40247C5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000076000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7042,7 +7049,7 @@
         <xdr:cNvPr id="119" name="CuadroTexto 118">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A8EE627A-17D0-4E29-8820-F4227DE17601}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000077000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7097,7 +7104,7 @@
         <xdr:cNvPr id="120" name="CuadroTexto 119">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9457EBD3-2A52-40A9-BF33-47E1D5E6B881}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000078000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7152,7 +7159,7 @@
         <xdr:cNvPr id="121" name="CuadroTexto 120">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{76E168C6-F378-47FF-8527-40CEF96B33D7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000079000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7207,7 +7214,7 @@
         <xdr:cNvPr id="122" name="CuadroTexto 121">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F844C091-2560-4301-BAF3-8068E0BAC55F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7262,7 +7269,7 @@
         <xdr:cNvPr id="123" name="CuadroTexto 122">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{35E230D2-65C6-4D3A-A509-7A30A1DD16A9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7317,7 +7324,7 @@
         <xdr:cNvPr id="124" name="CuadroTexto 123">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2EDBF8D8-7718-4726-A28C-81FA2ABDD45C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7372,7 +7379,7 @@
         <xdr:cNvPr id="125" name="CuadroTexto 124">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{68714B55-10B6-45CF-A3C1-0C0DAFC9FE2F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7427,7 +7434,7 @@
         <xdr:cNvPr id="126" name="CuadroTexto 125">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8CEFAF49-3ECC-48A2-AB1B-F4D575F95D93}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7482,7 +7489,7 @@
         <xdr:cNvPr id="127" name="CuadroTexto 126">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{1C11B0AF-A88B-425E-896C-38E47E95AE3C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7537,7 +7544,7 @@
         <xdr:cNvPr id="128" name="CuadroTexto 127">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C5ECD0FF-09D1-48E2-9B9E-3891CAAB79DF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000080000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7592,7 +7599,7 @@
         <xdr:cNvPr id="129" name="CuadroTexto 128">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A2655A27-C726-4427-8CDA-3F7CFB138A74}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000081000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7647,7 +7654,7 @@
         <xdr:cNvPr id="130" name="CuadroTexto 129">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A44DBF10-9E50-4594-B078-9E09C4F548CA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000082000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7702,7 +7709,7 @@
         <xdr:cNvPr id="131" name="CuadroTexto 130">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7139675D-98B0-457B-892F-D071C2122634}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000083000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7757,7 +7764,7 @@
         <xdr:cNvPr id="132" name="CuadroTexto 131">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2DE35652-3A7C-46D3-9CA6-8D8A23924C81}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000084000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7812,7 +7819,7 @@
         <xdr:cNvPr id="133" name="CuadroTexto 132">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0FAB82FB-B33D-496D-9C92-16657151B5B3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000085000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7867,7 +7874,7 @@
         <xdr:cNvPr id="134" name="CuadroTexto 133">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{969EEEFE-7928-4CEE-812D-8F79A8C4AFB7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000086000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7922,7 +7929,7 @@
         <xdr:cNvPr id="135" name="CuadroTexto 134">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8773DFFC-5EBA-4129-9396-58C5E3D0D6F1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000087000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7977,7 +7984,7 @@
         <xdr:cNvPr id="136" name="CuadroTexto 135">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7E0BCDA4-76CF-4653-9BD8-BB78D36A1B44}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000088000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8032,7 +8039,7 @@
         <xdr:cNvPr id="137" name="CuadroTexto 136">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{09D0F357-8BC0-426D-9C7F-36B33EA7EDB2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000089000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8087,7 +8094,7 @@
         <xdr:cNvPr id="138" name="CuadroTexto 137">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A75C6DE4-57F1-4925-907B-5D08A05ACAA6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8142,7 +8149,7 @@
         <xdr:cNvPr id="139" name="CuadroTexto 138">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9B75DCA7-709D-4185-BA61-FF14BE352E64}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8197,7 +8204,7 @@
         <xdr:cNvPr id="140" name="CuadroTexto 139">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{63EB681C-77E3-40BC-84F3-63CBD3DF2F86}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8252,7 +8259,7 @@
         <xdr:cNvPr id="141" name="CuadroTexto 140">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A0C51D34-3A7F-4FB6-9B6D-769D69362442}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8307,7 +8314,7 @@
         <xdr:cNvPr id="142" name="CuadroTexto 141">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8E4C4518-FB84-46F8-BEAA-57DF0BAB6F59}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8362,7 +8369,7 @@
         <xdr:cNvPr id="143" name="CuadroTexto 142">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6C9DB0F2-D7AA-4405-9DBA-8E26F40247C5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8417,7 +8424,7 @@
         <xdr:cNvPr id="144" name="CuadroTexto 143">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A8EE627A-17D0-4E29-8820-F4227DE17601}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000090000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8472,7 +8479,7 @@
         <xdr:cNvPr id="145" name="CuadroTexto 144">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{76E168C6-F378-47FF-8527-40CEF96B33D7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000091000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8527,7 +8534,7 @@
         <xdr:cNvPr id="146" name="CuadroTexto 145">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F844C091-2560-4301-BAF3-8068E0BAC55F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000092000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8582,7 +8589,7 @@
         <xdr:cNvPr id="147" name="CuadroTexto 146">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{68714B55-10B6-45CF-A3C1-0C0DAFC9FE2F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000093000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8637,7 +8644,7 @@
         <xdr:cNvPr id="148" name="CuadroTexto 147">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C5ECD0FF-09D1-48E2-9B9E-3891CAAB79DF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000094000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8692,7 +8699,7 @@
         <xdr:cNvPr id="149" name="CuadroTexto 148">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A2655A27-C726-4427-8CDA-3F7CFB138A74}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000095000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8747,7 +8754,7 @@
         <xdr:cNvPr id="150" name="CuadroTexto 149">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0FAB82FB-B33D-496D-9C92-16657151B5B3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000096000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8802,7 +8809,7 @@
         <xdr:cNvPr id="151" name="CuadroTexto 150">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{969EEEFE-7928-4CEE-812D-8F79A8C4AFB7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000097000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8857,7 +8864,7 @@
         <xdr:cNvPr id="152" name="CuadroTexto 151">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8773DFFC-5EBA-4129-9396-58C5E3D0D6F1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000098000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8912,7 +8919,7 @@
         <xdr:cNvPr id="153" name="CuadroTexto 152">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7E0BCDA4-76CF-4653-9BD8-BB78D36A1B44}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000099000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8967,7 +8974,7 @@
         <xdr:cNvPr id="154" name="CuadroTexto 153">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{09D0F357-8BC0-426D-9C7F-36B33EA7EDB2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00009A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9022,7 +9029,7 @@
         <xdr:cNvPr id="155" name="CuadroTexto 154">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{48D73822-C0EE-41FA-8C80-1DAA58F1467B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00009B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9077,7 +9084,7 @@
         <xdr:cNvPr id="156" name="CuadroTexto 155">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3036D108-B228-478C-9639-205717B86BBB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00009C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9132,7 +9139,7 @@
         <xdr:cNvPr id="157" name="CuadroTexto 156">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{44656067-2767-4EC9-A2B2-962F2E49D0EF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00009D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9187,7 +9194,7 @@
         <xdr:cNvPr id="158" name="CuadroTexto 157">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{B056B88E-0E38-4977-9A12-CEF45BB24762}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00009E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9242,7 +9249,7 @@
         <xdr:cNvPr id="159" name="CuadroTexto 158">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8DE03A80-E425-49E9-A027-E5B0C3DDA689}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00009F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9297,7 +9304,7 @@
         <xdr:cNvPr id="160" name="CuadroTexto 159">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{71C8BA03-006B-498A-BB9C-178E4AE79175}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A0000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9352,7 +9359,7 @@
         <xdr:cNvPr id="161" name="CuadroTexto 160">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{BA381632-1446-4A23-9D92-4D0728454AD7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A1000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9407,7 +9414,7 @@
         <xdr:cNvPr id="162" name="CuadroTexto 161">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{04931D77-294E-4693-95C7-CBEC805C7548}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A2000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9462,7 +9469,7 @@
         <xdr:cNvPr id="163" name="CuadroTexto 162">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4F31BCE1-E6DE-46F4-A930-6F5FB62D892A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A3000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9517,7 +9524,7 @@
         <xdr:cNvPr id="164" name="CuadroTexto 163">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F80CE3B0-F263-4250-BA3D-E78A258AF8D4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A4000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9572,7 +9579,7 @@
         <xdr:cNvPr id="165" name="CuadroTexto 164">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C2E51A83-E3A4-46A7-89AD-BAFFE8BFB462}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A5000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9627,7 +9634,7 @@
         <xdr:cNvPr id="166" name="CuadroTexto 165">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C8109D2F-25A0-4F45-BEE3-94EB0DC879ED}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A6000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9682,7 +9689,7 @@
         <xdr:cNvPr id="167" name="CuadroTexto 166">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6CF3DCB2-9CA0-4E78-9C53-C4627E6A2C82}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A7000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9737,7 +9744,7 @@
         <xdr:cNvPr id="168" name="CuadroTexto 167">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0D386A91-8EA4-4E28-8683-0FA15CD09032}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A8000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9792,7 +9799,7 @@
         <xdr:cNvPr id="169" name="CuadroTexto 168">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0B334990-CC91-4495-BC4C-171EB7FBE6FE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A9000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9847,7 +9854,7 @@
         <xdr:cNvPr id="170" name="CuadroTexto 169">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3FB7FB8B-7BBD-4779-B2EE-4A1F133D306B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000AA000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9902,7 +9909,7 @@
         <xdr:cNvPr id="171" name="CuadroTexto 170">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{954030D5-7DBB-4E2A-912E-ABD498AB02E9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000AB000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9957,7 +9964,7 @@
         <xdr:cNvPr id="172" name="CuadroTexto 171">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E0318F48-8E17-483F-BD39-1D251ADCF581}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000AC000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10012,7 +10019,7 @@
         <xdr:cNvPr id="173" name="CuadroTexto 172">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{06B68ED6-8772-4F26-A88E-6B215690F42D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000AD000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10067,7 +10074,7 @@
         <xdr:cNvPr id="174" name="CuadroTexto 173">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{355A8299-AB96-4F2C-8E15-194DDA6A1095}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000AE000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10122,7 +10129,7 @@
         <xdr:cNvPr id="175" name="CuadroTexto 174">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9222D574-8AA6-4339-B888-B90B573F0875}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000AF000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10177,7 +10184,7 @@
         <xdr:cNvPr id="176" name="CuadroTexto 175">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5C6DCA20-975D-426A-B5AE-98554BBAD33C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000B0000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10232,7 +10239,7 @@
         <xdr:cNvPr id="177" name="CuadroTexto 176">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{35F97302-5243-4622-A8AE-8654558AE536}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000B1000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10287,7 +10294,7 @@
         <xdr:cNvPr id="178" name="CuadroTexto 177">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{971E24A2-06B5-4991-B0A3-8CBAFBC3EE08}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000B2000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10342,7 +10349,7 @@
         <xdr:cNvPr id="179" name="CuadroTexto 178">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4D6564E3-B14D-46A1-B81F-69CCF7111617}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000B3000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10397,7 +10404,7 @@
         <xdr:cNvPr id="180" name="CuadroTexto 179">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{87D93D75-9DDD-47C1-BBE3-98B16379633E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000B4000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10452,7 +10459,7 @@
         <xdr:cNvPr id="181" name="CuadroTexto 180">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E22C7FD0-7AAD-4EAD-A0FC-DAFB34392E25}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000B5000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10507,7 +10514,7 @@
         <xdr:cNvPr id="182" name="CuadroTexto 181">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D225C2B8-1EDD-40D7-9C3C-741523E9E822}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000B6000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10562,7 +10569,7 @@
         <xdr:cNvPr id="183" name="CuadroTexto 182">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{ECC5E016-833E-47AF-BDA1-C693C795E1FD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000B7000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10617,7 +10624,7 @@
         <xdr:cNvPr id="184" name="CuadroTexto 183">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4E661821-E41D-409E-A479-1B1EDEE26329}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000B8000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10672,7 +10679,7 @@
         <xdr:cNvPr id="185" name="CuadroTexto 184">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6EF617BF-FA51-4493-BD85-407E4691D777}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000B9000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10727,7 +10734,7 @@
         <xdr:cNvPr id="186" name="CuadroTexto 185">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C69510D8-31CD-4D62-9B5F-0B3C65DBD694}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000BA000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10782,7 +10789,7 @@
         <xdr:cNvPr id="187" name="CuadroTexto 186">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E25F6EE1-DB29-472A-911B-425BDAE8F999}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000BB000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10837,7 +10844,7 @@
         <xdr:cNvPr id="188" name="CuadroTexto 187">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6ED5C0E6-2818-48E4-91D1-FE29F079AFA6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000BC000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10892,7 +10899,7 @@
         <xdr:cNvPr id="189" name="CuadroTexto 188">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2C8E96A3-17CB-4B71-86BB-E36B4F02E426}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000BD000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10947,7 +10954,7 @@
         <xdr:cNvPr id="190" name="CuadroTexto 189">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D27999A5-27D7-4D7A-9482-4457AC72810D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000BE000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11002,7 +11009,7 @@
         <xdr:cNvPr id="191" name="CuadroTexto 190">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0A48F321-6B96-47D0-A838-CB5DB8C655E8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000BF000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11057,7 +11064,7 @@
         <xdr:cNvPr id="192" name="CuadroTexto 191">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{DCC66F88-76CD-4D40-83F1-40876A4B75EC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000C0000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11112,7 +11119,7 @@
         <xdr:cNvPr id="193" name="CuadroTexto 192">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2FA5E455-4F77-4FD5-B8C1-8D79C3285A2E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000C1000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11167,7 +11174,7 @@
         <xdr:cNvPr id="194" name="CuadroTexto 193">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{27D86713-7948-42F7-8B6F-D9A8009B6960}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000C2000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11222,7 +11229,7 @@
         <xdr:cNvPr id="195" name="CuadroTexto 194">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5C6DCA20-975D-426A-B5AE-98554BBAD33C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000C3000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11277,7 +11284,7 @@
         <xdr:cNvPr id="196" name="CuadroTexto 195">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{35F97302-5243-4622-A8AE-8654558AE536}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000C4000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11332,7 +11339,7 @@
         <xdr:cNvPr id="197" name="CuadroTexto 196">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{971E24A2-06B5-4991-B0A3-8CBAFBC3EE08}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000C5000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11387,7 +11394,7 @@
         <xdr:cNvPr id="198" name="CuadroTexto 197">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4D6564E3-B14D-46A1-B81F-69CCF7111617}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000C6000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11442,7 +11449,7 @@
         <xdr:cNvPr id="199" name="CuadroTexto 198">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E25F6EE1-DB29-472A-911B-425BDAE8F999}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000C7000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11497,7 +11504,7 @@
         <xdr:cNvPr id="200" name="CuadroTexto 199">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{DCC66F88-76CD-4D40-83F1-40876A4B75EC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000C8000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11552,7 +11559,7 @@
         <xdr:cNvPr id="201" name="CuadroTexto 200">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2FA5E455-4F77-4FD5-B8C1-8D79C3285A2E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000C9000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11607,7 +11614,7 @@
         <xdr:cNvPr id="202" name="CuadroTexto 201">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F80CE3B0-F263-4250-BA3D-E78A258AF8D4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000CA000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11662,7 +11669,7 @@
         <xdr:cNvPr id="203" name="CuadroTexto 202">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C2E51A83-E3A4-46A7-89AD-BAFFE8BFB462}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000CB000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11717,7 +11724,7 @@
         <xdr:cNvPr id="204" name="CuadroTexto 203">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C8109D2F-25A0-4F45-BEE3-94EB0DC879ED}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000CC000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11772,7 +11779,7 @@
         <xdr:cNvPr id="205" name="CuadroTexto 204">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6CF3DCB2-9CA0-4E78-9C53-C4627E6A2C82}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000CD000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11827,7 +11834,7 @@
         <xdr:cNvPr id="206" name="CuadroTexto 205">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0D386A91-8EA4-4E28-8683-0FA15CD09032}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000CE000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11882,7 +11889,7 @@
         <xdr:cNvPr id="207" name="CuadroTexto 206">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0B334990-CC91-4495-BC4C-171EB7FBE6FE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000CF000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11937,7 +11944,7 @@
         <xdr:cNvPr id="208" name="CuadroTexto 207">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3FB7FB8B-7BBD-4779-B2EE-4A1F133D306B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000D0000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11992,7 +11999,7 @@
         <xdr:cNvPr id="209" name="CuadroTexto 208">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{954030D5-7DBB-4E2A-912E-ABD498AB02E9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000D1000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12047,7 +12054,7 @@
         <xdr:cNvPr id="210" name="CuadroTexto 209">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E0318F48-8E17-483F-BD39-1D251ADCF581}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000D2000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12102,7 +12109,7 @@
         <xdr:cNvPr id="211" name="CuadroTexto 210">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{06B68ED6-8772-4F26-A88E-6B215690F42D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000D3000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12157,7 +12164,7 @@
         <xdr:cNvPr id="212" name="CuadroTexto 211">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{355A8299-AB96-4F2C-8E15-194DDA6A1095}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000D4000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12212,7 +12219,7 @@
         <xdr:cNvPr id="213" name="CuadroTexto 212">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9222D574-8AA6-4339-B888-B90B573F0875}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000D5000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12267,7 +12274,7 @@
         <xdr:cNvPr id="214" name="CuadroTexto 213">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D225C2B8-1EDD-40D7-9C3C-741523E9E822}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000D6000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12322,7 +12329,7 @@
         <xdr:cNvPr id="215" name="CuadroTexto 214">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{ECC5E016-833E-47AF-BDA1-C693C795E1FD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000D7000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12377,7 +12384,7 @@
         <xdr:cNvPr id="216" name="CuadroTexto 215">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A75C6DE4-57F1-4925-907B-5D08A05ACAA6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000D8000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12432,7 +12439,7 @@
         <xdr:cNvPr id="217" name="CuadroTexto 216">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9B75DCA7-709D-4185-BA61-FF14BE352E64}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000D9000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12487,7 +12494,7 @@
         <xdr:cNvPr id="218" name="CuadroTexto 217">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2C8E96A3-17CB-4B71-86BB-E36B4F02E426}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000DA000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12542,7 +12549,7 @@
         <xdr:cNvPr id="219" name="CuadroTexto 218">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D27999A5-27D7-4D7A-9482-4457AC72810D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000DB000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12597,7 +12604,7 @@
         <xdr:cNvPr id="220" name="CuadroTexto 219">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{63EB681C-77E3-40BC-84F3-63CBD3DF2F86}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000DC000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12652,7 +12659,7 @@
         <xdr:cNvPr id="221" name="CuadroTexto 220">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0A48F321-6B96-47D0-A838-CB5DB8C655E8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000DD000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12707,7 +12714,7 @@
         <xdr:cNvPr id="222" name="CuadroTexto 221">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A0C51D34-3A7F-4FB6-9B6D-769D69362442}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000DE000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12762,7 +12769,7 @@
         <xdr:cNvPr id="223" name="CuadroTexto 222">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8E4C4518-FB84-46F8-BEAA-57DF0BAB6F59}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000DF000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12817,7 +12824,7 @@
         <xdr:cNvPr id="224" name="CuadroTexto 223">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6C9DB0F2-D7AA-4405-9DBA-8E26F40247C5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000E0000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12872,7 +12879,7 @@
         <xdr:cNvPr id="225" name="CuadroTexto 224">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A8EE627A-17D0-4E29-8820-F4227DE17601}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000E1000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12927,7 +12934,7 @@
         <xdr:cNvPr id="226" name="CuadroTexto 225">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{76E168C6-F378-47FF-8527-40CEF96B33D7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000E2000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12982,7 +12989,7 @@
         <xdr:cNvPr id="227" name="CuadroTexto 226">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F844C091-2560-4301-BAF3-8068E0BAC55F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000E3000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13037,7 +13044,7 @@
         <xdr:cNvPr id="228" name="CuadroTexto 227">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{68714B55-10B6-45CF-A3C1-0C0DAFC9FE2F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000E4000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13092,7 +13099,7 @@
         <xdr:cNvPr id="229" name="CuadroTexto 228">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C5ECD0FF-09D1-48E2-9B9E-3891CAAB79DF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000E5000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13147,7 +13154,7 @@
         <xdr:cNvPr id="230" name="CuadroTexto 229">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A2655A27-C726-4427-8CDA-3F7CFB138A74}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000E6000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13202,7 +13209,7 @@
         <xdr:cNvPr id="231" name="CuadroTexto 230">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0FAB82FB-B33D-496D-9C92-16657151B5B3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000E7000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13257,7 +13264,7 @@
         <xdr:cNvPr id="232" name="CuadroTexto 231">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{969EEEFE-7928-4CEE-812D-8F79A8C4AFB7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000E8000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13312,7 +13319,7 @@
         <xdr:cNvPr id="233" name="CuadroTexto 232">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8773DFFC-5EBA-4129-9396-58C5E3D0D6F1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000E9000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13367,7 +13374,7 @@
         <xdr:cNvPr id="234" name="CuadroTexto 233">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7E0BCDA4-76CF-4653-9BD8-BB78D36A1B44}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000EA000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13422,7 +13429,7 @@
         <xdr:cNvPr id="235" name="CuadroTexto 234">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{09D0F357-8BC0-426D-9C7F-36B33EA7EDB2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000EB000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13477,7 +13484,7 @@
         <xdr:cNvPr id="236" name="CuadroTexto 235">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E22C7FD0-7AAD-4EAD-A0FC-DAFB34392E25}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000EC000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13532,7 +13539,7 @@
         <xdr:cNvPr id="237" name="CuadroTexto 236">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E25F6EE1-DB29-472A-911B-425BDAE8F999}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000ED000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13587,7 +13594,7 @@
         <xdr:cNvPr id="238" name="CuadroTexto 237">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6ED5C0E6-2818-48E4-91D1-FE29F079AFA6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000EE000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13642,7 +13649,7 @@
         <xdr:cNvPr id="239" name="CuadroTexto 238">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{DCC66F88-76CD-4D40-83F1-40876A4B75EC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000EF000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13697,7 +13704,7 @@
         <xdr:cNvPr id="240" name="CuadroTexto 239">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2FA5E455-4F77-4FD5-B8C1-8D79C3285A2E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000F0000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13752,7 +13759,7 @@
         <xdr:cNvPr id="241" name="CuadroTexto 240">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{27D86713-7948-42F7-8B6F-D9A8009B6960}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000F1000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13807,7 +13814,7 @@
         <xdr:cNvPr id="242" name="CuadroTexto 241">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E25F6EE1-DB29-472A-911B-425BDAE8F999}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000F2000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13862,7 +13869,7 @@
         <xdr:cNvPr id="243" name="CuadroTexto 242">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{DCC66F88-76CD-4D40-83F1-40876A4B75EC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000F3000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13917,7 +13924,7 @@
         <xdr:cNvPr id="244" name="CuadroTexto 243">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2FA5E455-4F77-4FD5-B8C1-8D79C3285A2E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000F4000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13972,7 +13979,7 @@
         <xdr:cNvPr id="245" name="CuadroTexto 244">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D225C2B8-1EDD-40D7-9C3C-741523E9E822}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000F5000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14027,7 +14034,7 @@
         <xdr:cNvPr id="246" name="CuadroTexto 245">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{ECC5E016-833E-47AF-BDA1-C693C795E1FD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000F6000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14082,7 +14089,7 @@
         <xdr:cNvPr id="247" name="CuadroTexto 246">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A75C6DE4-57F1-4925-907B-5D08A05ACAA6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000F7000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14137,7 +14144,7 @@
         <xdr:cNvPr id="248" name="CuadroTexto 247">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9B75DCA7-709D-4185-BA61-FF14BE352E64}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000F8000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14192,7 +14199,7 @@
         <xdr:cNvPr id="249" name="CuadroTexto 248">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2C8E96A3-17CB-4B71-86BB-E36B4F02E426}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000F9000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14247,7 +14254,7 @@
         <xdr:cNvPr id="250" name="CuadroTexto 249">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D27999A5-27D7-4D7A-9482-4457AC72810D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000FA000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14302,7 +14309,7 @@
         <xdr:cNvPr id="251" name="CuadroTexto 250">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{63EB681C-77E3-40BC-84F3-63CBD3DF2F86}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000FB000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14357,7 +14364,7 @@
         <xdr:cNvPr id="252" name="CuadroTexto 251">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0A48F321-6B96-47D0-A838-CB5DB8C655E8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000FC000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14412,7 +14419,7 @@
         <xdr:cNvPr id="253" name="CuadroTexto 252">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A0C51D34-3A7F-4FB6-9B6D-769D69362442}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000FD000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14467,7 +14474,7 @@
         <xdr:cNvPr id="254" name="CuadroTexto 253">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8E4C4518-FB84-46F8-BEAA-57DF0BAB6F59}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000FE000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14522,7 +14529,7 @@
         <xdr:cNvPr id="255" name="CuadroTexto 254">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6C9DB0F2-D7AA-4405-9DBA-8E26F40247C5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000FF000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14577,7 +14584,7 @@
         <xdr:cNvPr id="256" name="CuadroTexto 255">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A8EE627A-17D0-4E29-8820-F4227DE17601}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000000010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14632,7 +14639,7 @@
         <xdr:cNvPr id="257" name="CuadroTexto 256">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{76E168C6-F378-47FF-8527-40CEF96B33D7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14687,7 +14694,7 @@
         <xdr:cNvPr id="258" name="CuadroTexto 257">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F844C091-2560-4301-BAF3-8068E0BAC55F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14742,7 +14749,7 @@
         <xdr:cNvPr id="259" name="CuadroTexto 258">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{68714B55-10B6-45CF-A3C1-0C0DAFC9FE2F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14797,7 +14804,7 @@
         <xdr:cNvPr id="260" name="CuadroTexto 259">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C5ECD0FF-09D1-48E2-9B9E-3891CAAB79DF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14852,7 +14859,7 @@
         <xdr:cNvPr id="261" name="CuadroTexto 260">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A2655A27-C726-4427-8CDA-3F7CFB138A74}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14907,7 +14914,7 @@
         <xdr:cNvPr id="262" name="CuadroTexto 261">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0FAB82FB-B33D-496D-9C92-16657151B5B3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14962,7 +14969,7 @@
         <xdr:cNvPr id="263" name="CuadroTexto 262">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{969EEEFE-7928-4CEE-812D-8F79A8C4AFB7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -15017,7 +15024,7 @@
         <xdr:cNvPr id="264" name="CuadroTexto 263">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8773DFFC-5EBA-4129-9396-58C5E3D0D6F1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -15072,7 +15079,7 @@
         <xdr:cNvPr id="265" name="CuadroTexto 264">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7E0BCDA4-76CF-4653-9BD8-BB78D36A1B44}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -15127,7 +15134,7 @@
         <xdr:cNvPr id="266" name="CuadroTexto 265">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{09D0F357-8BC0-426D-9C7F-36B33EA7EDB2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -15182,7 +15189,7 @@
         <xdr:cNvPr id="267" name="CuadroTexto 266">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E22C7FD0-7AAD-4EAD-A0FC-DAFB34392E25}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -15237,7 +15244,7 @@
         <xdr:cNvPr id="268" name="CuadroTexto 267">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E25F6EE1-DB29-472A-911B-425BDAE8F999}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -15292,7 +15299,7 @@
         <xdr:cNvPr id="269" name="CuadroTexto 268">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6ED5C0E6-2818-48E4-91D1-FE29F079AFA6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -15347,7 +15354,7 @@
         <xdr:cNvPr id="270" name="CuadroTexto 269">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{DCC66F88-76CD-4D40-83F1-40876A4B75EC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -15402,7 +15409,7 @@
         <xdr:cNvPr id="271" name="CuadroTexto 270">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2FA5E455-4F77-4FD5-B8C1-8D79C3285A2E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000F010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -15457,7 +15464,7 @@
         <xdr:cNvPr id="272" name="CuadroTexto 271">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{27D86713-7948-42F7-8B6F-D9A8009B6960}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000010010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -15512,7 +15519,7 @@
         <xdr:cNvPr id="273" name="CuadroTexto 272">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E25F6EE1-DB29-472A-911B-425BDAE8F999}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000011010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -15567,7 +15574,7 @@
         <xdr:cNvPr id="274" name="CuadroTexto 273">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{DCC66F88-76CD-4D40-83F1-40876A4B75EC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000012010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -15622,7 +15629,7 @@
         <xdr:cNvPr id="275" name="CuadroTexto 274">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2FA5E455-4F77-4FD5-B8C1-8D79C3285A2E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000013010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -15677,7 +15684,7 @@
         <xdr:cNvPr id="276" name="CuadroTexto 275">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E22C7FD0-7AAD-4EAD-A0FC-DAFB34392E25}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000014010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -15732,7 +15739,7 @@
         <xdr:cNvPr id="277" name="CuadroTexto 276">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D225C2B8-1EDD-40D7-9C3C-741523E9E822}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000015010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -15787,7 +15794,7 @@
         <xdr:cNvPr id="278" name="CuadroTexto 277">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{ECC5E016-833E-47AF-BDA1-C693C795E1FD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000016010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -15842,7 +15849,7 @@
         <xdr:cNvPr id="279" name="CuadroTexto 278">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6ED5C0E6-2818-48E4-91D1-FE29F079AFA6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000017010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -15897,7 +15904,7 @@
         <xdr:cNvPr id="280" name="CuadroTexto 279">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2C8E96A3-17CB-4B71-86BB-E36B4F02E426}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000018010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -15952,7 +15959,7 @@
         <xdr:cNvPr id="281" name="CuadroTexto 280">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D27999A5-27D7-4D7A-9482-4457AC72810D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000019010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -16007,7 +16014,7 @@
         <xdr:cNvPr id="282" name="CuadroTexto 281">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0A48F321-6B96-47D0-A838-CB5DB8C655E8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001A010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -16062,7 +16069,7 @@
         <xdr:cNvPr id="283" name="CuadroTexto 282">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{27D86713-7948-42F7-8B6F-D9A8009B6960}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001B010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -16117,7 +16124,7 @@
         <xdr:cNvPr id="284" name="CuadroTexto 283">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F5FA9D63-02F2-4083-AFEA-BC85CBB0BBF9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001C010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -16172,7 +16179,7 @@
         <xdr:cNvPr id="285" name="CuadroTexto 284">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{1AC1FF37-2A96-4CA4-A4D3-9E1A67778BA3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001D010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -16227,7 +16234,7 @@
         <xdr:cNvPr id="286" name="CuadroTexto 285">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D5E4C9FE-5389-4D27-8E73-8AF1C65D7DAF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001E010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -16282,7 +16289,7 @@
         <xdr:cNvPr id="287" name="CuadroTexto 286">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A5DE5D70-BA42-4918-BFB8-322D1A83003D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001F010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -16337,7 +16344,7 @@
         <xdr:cNvPr id="288" name="CuadroTexto 287">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{B1618B97-90B2-455C-9F5A-44BE21DCEC37}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000020010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -16392,7 +16399,7 @@
         <xdr:cNvPr id="289" name="CuadroTexto 288">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4C0C4DE1-47C0-4F71-AB45-AF1CAEB85E58}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000021010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -16447,7 +16454,7 @@
         <xdr:cNvPr id="290" name="CuadroTexto 289">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{52060FAA-DF77-48C2-9133-177B4658C899}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000022010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -16502,7 +16509,7 @@
         <xdr:cNvPr id="291" name="CuadroTexto 290">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9E2C4242-91E4-4B93-854C-EED968965F83}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000023010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -16557,7 +16564,7 @@
         <xdr:cNvPr id="292" name="CuadroTexto 291">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{299FC220-8A4C-49BE-8ED4-F18E0A39BBCA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000024010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -16612,7 +16619,7 @@
         <xdr:cNvPr id="293" name="CuadroTexto 292">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{03B79463-C31E-4895-9F68-D895A5A30585}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000025010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -16667,7 +16674,7 @@
         <xdr:cNvPr id="294" name="CuadroTexto 293">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6353DFA9-437C-4ECB-89B6-46D6602BD2DB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000026010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -16722,7 +16729,7 @@
         <xdr:cNvPr id="295" name="CuadroTexto 294">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{70EE90A1-B2BD-49F9-AA5A-D37A49E13FDA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000027010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -16777,7 +16784,7 @@
         <xdr:cNvPr id="296" name="CuadroTexto 295">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E71FAC61-1CC2-4ABA-BA98-C03F5DDFB6C4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000028010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -16832,7 +16839,7 @@
         <xdr:cNvPr id="297" name="CuadroTexto 296">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{868531C5-7CFC-4BFD-9745-A30B2D199BB9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000029010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -16887,7 +16894,7 @@
         <xdr:cNvPr id="298" name="CuadroTexto 297">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C9A975DC-E577-468E-B791-D92EA0A7C22C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002A010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -16942,7 +16949,7 @@
         <xdr:cNvPr id="299" name="CuadroTexto 298">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E85028FC-C066-407A-A9CA-617CAACBD592}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002B010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -16997,7 +17004,7 @@
         <xdr:cNvPr id="300" name="CuadroTexto 299">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D35DE71D-3A0C-4934-9A7F-8E95D268A3E6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002C010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17052,7 +17059,7 @@
         <xdr:cNvPr id="301" name="CuadroTexto 300">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E25F6EE1-DB29-472A-911B-425BDAE8F999}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002D010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17107,7 +17114,7 @@
         <xdr:cNvPr id="302" name="CuadroTexto 301">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{DCC66F88-76CD-4D40-83F1-40876A4B75EC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002E010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17162,7 +17169,7 @@
         <xdr:cNvPr id="303" name="CuadroTexto 302">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2FA5E455-4F77-4FD5-B8C1-8D79C3285A2E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002F010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17217,7 +17224,7 @@
         <xdr:cNvPr id="304" name="CuadroTexto 303">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E22C7FD0-7AAD-4EAD-A0FC-DAFB34392E25}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000030010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17272,7 +17279,7 @@
         <xdr:cNvPr id="305" name="CuadroTexto 304">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D225C2B8-1EDD-40D7-9C3C-741523E9E822}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000031010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17327,7 +17334,7 @@
         <xdr:cNvPr id="306" name="CuadroTexto 305">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{ECC5E016-833E-47AF-BDA1-C693C795E1FD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000032010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17382,7 +17389,7 @@
         <xdr:cNvPr id="307" name="CuadroTexto 306">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6ED5C0E6-2818-48E4-91D1-FE29F079AFA6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000033010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17437,7 +17444,7 @@
         <xdr:cNvPr id="308" name="CuadroTexto 307">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2C8E96A3-17CB-4B71-86BB-E36B4F02E426}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000034010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17492,7 +17499,7 @@
         <xdr:cNvPr id="309" name="CuadroTexto 308">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D27999A5-27D7-4D7A-9482-4457AC72810D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000035010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17547,7 +17554,7 @@
         <xdr:cNvPr id="310" name="CuadroTexto 309">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0A48F321-6B96-47D0-A838-CB5DB8C655E8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000036010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17602,7 +17609,7 @@
         <xdr:cNvPr id="311" name="CuadroTexto 310">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{27D86713-7948-42F7-8B6F-D9A8009B6960}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000037010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17657,7 +17664,7 @@
         <xdr:cNvPr id="312" name="CuadroTexto 311">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E25F6EE1-DB29-472A-911B-425BDAE8F999}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000038010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17712,7 +17719,7 @@
         <xdr:cNvPr id="313" name="CuadroTexto 312">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{DCC66F88-76CD-4D40-83F1-40876A4B75EC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000039010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17767,7 +17774,7 @@
         <xdr:cNvPr id="314" name="CuadroTexto 313">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2FA5E455-4F77-4FD5-B8C1-8D79C3285A2E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003A010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17822,7 +17829,7 @@
         <xdr:cNvPr id="315" name="CuadroTexto 314">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D225C2B8-1EDD-40D7-9C3C-741523E9E822}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003B010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17877,7 +17884,7 @@
         <xdr:cNvPr id="316" name="CuadroTexto 315">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{ECC5E016-833E-47AF-BDA1-C693C795E1FD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17932,7 +17939,7 @@
         <xdr:cNvPr id="317" name="CuadroTexto 316">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2C8E96A3-17CB-4B71-86BB-E36B4F02E426}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003D010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17987,7 +17994,7 @@
         <xdr:cNvPr id="318" name="CuadroTexto 317">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D27999A5-27D7-4D7A-9482-4457AC72810D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18042,7 +18049,7 @@
         <xdr:cNvPr id="319" name="CuadroTexto 318">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0A48F321-6B96-47D0-A838-CB5DB8C655E8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003F010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18097,7 +18104,7 @@
         <xdr:cNvPr id="320" name="CuadroTexto 319">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E25F6EE1-DB29-472A-911B-425BDAE8F999}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000040010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18152,7 +18159,7 @@
         <xdr:cNvPr id="321" name="CuadroTexto 320">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{DCC66F88-76CD-4D40-83F1-40876A4B75EC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000041010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18207,7 +18214,7 @@
         <xdr:cNvPr id="322" name="CuadroTexto 321">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2FA5E455-4F77-4FD5-B8C1-8D79C3285A2E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000042010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18262,7 +18269,7 @@
         <xdr:cNvPr id="323" name="CuadroTexto 322">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9457EBD3-2A52-40A9-BF33-47E1D5E6B881}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000043010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18317,7 +18324,7 @@
         <xdr:cNvPr id="324" name="CuadroTexto 323">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{35E230D2-65C6-4D3A-A509-7A30A1DD16A9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18372,7 +18379,7 @@
         <xdr:cNvPr id="325" name="CuadroTexto 324">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2EDBF8D8-7718-4726-A28C-81FA2ABDD45C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18427,7 +18434,7 @@
         <xdr:cNvPr id="326" name="CuadroTexto 325">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8CEFAF49-3ECC-48A2-AB1B-F4D575F95D93}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18482,7 +18489,7 @@
         <xdr:cNvPr id="327" name="CuadroTexto 326">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{1C11B0AF-A88B-425E-896C-38E47E95AE3C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18537,7 +18544,7 @@
         <xdr:cNvPr id="328" name="CuadroTexto 327">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A44DBF10-9E50-4594-B078-9E09C4F548CA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18592,7 +18599,7 @@
         <xdr:cNvPr id="329" name="CuadroTexto 328">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7139675D-98B0-457B-892F-D071C2122634}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18647,7 +18654,7 @@
         <xdr:cNvPr id="330" name="CuadroTexto 329">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2DE35652-3A7C-46D3-9CA6-8D8A23924C81}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18702,7 +18709,7 @@
         <xdr:cNvPr id="331" name="CuadroTexto 330">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A75C6DE4-57F1-4925-907B-5D08A05ACAA6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18757,7 +18764,7 @@
         <xdr:cNvPr id="332" name="CuadroTexto 331">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9B75DCA7-709D-4185-BA61-FF14BE352E64}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18812,7 +18819,7 @@
         <xdr:cNvPr id="333" name="CuadroTexto 332">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{63EB681C-77E3-40BC-84F3-63CBD3DF2F86}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18867,7 +18874,7 @@
         <xdr:cNvPr id="334" name="CuadroTexto 333">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A0C51D34-3A7F-4FB6-9B6D-769D69362442}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18922,7 +18929,7 @@
         <xdr:cNvPr id="335" name="CuadroTexto 334">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8E4C4518-FB84-46F8-BEAA-57DF0BAB6F59}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18977,7 +18984,7 @@
         <xdr:cNvPr id="336" name="CuadroTexto 335">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6C9DB0F2-D7AA-4405-9DBA-8E26F40247C5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19032,7 +19039,7 @@
         <xdr:cNvPr id="337" name="CuadroTexto 336">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A8EE627A-17D0-4E29-8820-F4227DE17601}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19087,7 +19094,7 @@
         <xdr:cNvPr id="338" name="CuadroTexto 337">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{76E168C6-F378-47FF-8527-40CEF96B33D7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19142,7 +19149,7 @@
         <xdr:cNvPr id="339" name="CuadroTexto 338">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F844C091-2560-4301-BAF3-8068E0BAC55F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19197,7 +19204,7 @@
         <xdr:cNvPr id="340" name="CuadroTexto 339">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{68714B55-10B6-45CF-A3C1-0C0DAFC9FE2F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19252,7 +19259,7 @@
         <xdr:cNvPr id="341" name="CuadroTexto 340">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C5ECD0FF-09D1-48E2-9B9E-3891CAAB79DF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19307,7 +19314,7 @@
         <xdr:cNvPr id="342" name="CuadroTexto 341">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A2655A27-C726-4427-8CDA-3F7CFB138A74}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19362,7 +19369,7 @@
         <xdr:cNvPr id="343" name="CuadroTexto 342">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0FAB82FB-B33D-496D-9C92-16657151B5B3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000057010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19417,7 +19424,7 @@
         <xdr:cNvPr id="344" name="CuadroTexto 343">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{969EEEFE-7928-4CEE-812D-8F79A8C4AFB7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19472,7 +19479,7 @@
         <xdr:cNvPr id="345" name="CuadroTexto 344">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8773DFFC-5EBA-4129-9396-58C5E3D0D6F1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19527,7 +19534,7 @@
         <xdr:cNvPr id="346" name="CuadroTexto 345">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7E0BCDA4-76CF-4653-9BD8-BB78D36A1B44}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19582,7 +19589,7 @@
         <xdr:cNvPr id="347" name="CuadroTexto 346">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{09D0F357-8BC0-426D-9C7F-36B33EA7EDB2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19637,7 +19644,7 @@
         <xdr:cNvPr id="348" name="CuadroTexto 347">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A75C6DE4-57F1-4925-907B-5D08A05ACAA6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19692,7 +19699,7 @@
         <xdr:cNvPr id="349" name="CuadroTexto 348">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9B75DCA7-709D-4185-BA61-FF14BE352E64}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19747,7 +19754,7 @@
         <xdr:cNvPr id="350" name="CuadroTexto 349">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{63EB681C-77E3-40BC-84F3-63CBD3DF2F86}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19802,7 +19809,7 @@
         <xdr:cNvPr id="351" name="CuadroTexto 350">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A0C51D34-3A7F-4FB6-9B6D-769D69362442}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19857,7 +19864,7 @@
         <xdr:cNvPr id="352" name="CuadroTexto 351">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8E4C4518-FB84-46F8-BEAA-57DF0BAB6F59}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19912,7 +19919,7 @@
         <xdr:cNvPr id="353" name="CuadroTexto 352">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6C9DB0F2-D7AA-4405-9DBA-8E26F40247C5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19967,7 +19974,7 @@
         <xdr:cNvPr id="354" name="CuadroTexto 353">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A8EE627A-17D0-4E29-8820-F4227DE17601}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -20022,7 +20029,7 @@
         <xdr:cNvPr id="355" name="CuadroTexto 354">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{76E168C6-F378-47FF-8527-40CEF96B33D7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -20077,7 +20084,7 @@
         <xdr:cNvPr id="356" name="CuadroTexto 355">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F844C091-2560-4301-BAF3-8068E0BAC55F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -20132,7 +20139,7 @@
         <xdr:cNvPr id="357" name="CuadroTexto 356">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{68714B55-10B6-45CF-A3C1-0C0DAFC9FE2F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -20187,7 +20194,7 @@
         <xdr:cNvPr id="358" name="CuadroTexto 357">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C5ECD0FF-09D1-48E2-9B9E-3891CAAB79DF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000066010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -20242,7 +20249,7 @@
         <xdr:cNvPr id="359" name="CuadroTexto 358">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A2655A27-C726-4427-8CDA-3F7CFB138A74}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -20297,7 +20304,7 @@
         <xdr:cNvPr id="360" name="CuadroTexto 359">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0FAB82FB-B33D-496D-9C92-16657151B5B3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -20352,7 +20359,7 @@
         <xdr:cNvPr id="361" name="CuadroTexto 360">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{969EEEFE-7928-4CEE-812D-8F79A8C4AFB7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -20407,7 +20414,7 @@
         <xdr:cNvPr id="362" name="CuadroTexto 361">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8773DFFC-5EBA-4129-9396-58C5E3D0D6F1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -20462,7 +20469,7 @@
         <xdr:cNvPr id="363" name="CuadroTexto 362">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7E0BCDA4-76CF-4653-9BD8-BB78D36A1B44}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -20517,7 +20524,7 @@
         <xdr:cNvPr id="364" name="CuadroTexto 363">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{09D0F357-8BC0-426D-9C7F-36B33EA7EDB2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -20572,7 +20579,7 @@
         <xdr:cNvPr id="365" name="CuadroTexto 364">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E22C7FD0-7AAD-4EAD-A0FC-DAFB34392E25}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006D010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -20627,7 +20634,7 @@
         <xdr:cNvPr id="366" name="CuadroTexto 365">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6ED5C0E6-2818-48E4-91D1-FE29F079AFA6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006E010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -20682,7 +20689,7 @@
         <xdr:cNvPr id="367" name="CuadroTexto 366">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{27D86713-7948-42F7-8B6F-D9A8009B6960}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006F010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -20737,7 +20744,7 @@
         <xdr:cNvPr id="368" name="CuadroTexto 367">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E25F6EE1-DB29-472A-911B-425BDAE8F999}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000070010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -20792,7 +20799,7 @@
         <xdr:cNvPr id="369" name="CuadroTexto 368">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{DCC66F88-76CD-4D40-83F1-40876A4B75EC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000071010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -20847,7 +20854,7 @@
         <xdr:cNvPr id="370" name="CuadroTexto 369">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2FA5E455-4F77-4FD5-B8C1-8D79C3285A2E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000072010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -20902,7 +20909,7 @@
         <xdr:cNvPr id="371" name="CuadroTexto 370">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E22C7FD0-7AAD-4EAD-A0FC-DAFB34392E25}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000073010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -20957,7 +20964,7 @@
         <xdr:cNvPr id="372" name="CuadroTexto 371">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6ED5C0E6-2818-48E4-91D1-FE29F079AFA6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000074010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21012,7 +21019,7 @@
         <xdr:cNvPr id="373" name="CuadroTexto 372">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{27D86713-7948-42F7-8B6F-D9A8009B6960}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000075010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21067,7 +21074,7 @@
         <xdr:cNvPr id="374" name="CuadroTexto 373">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F5FA9D63-02F2-4083-AFEA-BC85CBB0BBF9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000076010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21122,7 +21129,7 @@
         <xdr:cNvPr id="375" name="CuadroTexto 374">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{1AC1FF37-2A96-4CA4-A4D3-9E1A67778BA3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000077010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21177,7 +21184,7 @@
         <xdr:cNvPr id="376" name="CuadroTexto 375">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D5E4C9FE-5389-4D27-8E73-8AF1C65D7DAF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000078010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21232,7 +21239,7 @@
         <xdr:cNvPr id="377" name="CuadroTexto 376">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A5DE5D70-BA42-4918-BFB8-322D1A83003D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000079010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21287,7 +21294,7 @@
         <xdr:cNvPr id="378" name="CuadroTexto 377">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{B1618B97-90B2-455C-9F5A-44BE21DCEC37}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007A010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21342,7 +21349,7 @@
         <xdr:cNvPr id="379" name="CuadroTexto 378">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4C0C4DE1-47C0-4F71-AB45-AF1CAEB85E58}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007B010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21397,7 +21404,7 @@
         <xdr:cNvPr id="380" name="CuadroTexto 379">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{52060FAA-DF77-48C2-9133-177B4658C899}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007C010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21452,7 +21459,7 @@
         <xdr:cNvPr id="381" name="CuadroTexto 380">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9E2C4242-91E4-4B93-854C-EED968965F83}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007D010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21507,7 +21514,7 @@
         <xdr:cNvPr id="382" name="CuadroTexto 381">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{299FC220-8A4C-49BE-8ED4-F18E0A39BBCA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007E010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21562,7 +21569,7 @@
         <xdr:cNvPr id="383" name="CuadroTexto 382">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{03B79463-C31E-4895-9F68-D895A5A30585}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007F010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21617,7 +21624,7 @@
         <xdr:cNvPr id="384" name="CuadroTexto 383">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6353DFA9-437C-4ECB-89B6-46D6602BD2DB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000080010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21672,7 +21679,7 @@
         <xdr:cNvPr id="385" name="CuadroTexto 384">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{70EE90A1-B2BD-49F9-AA5A-D37A49E13FDA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000081010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21727,7 +21734,7 @@
         <xdr:cNvPr id="386" name="CuadroTexto 385">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E71FAC61-1CC2-4ABA-BA98-C03F5DDFB6C4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000082010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21782,7 +21789,7 @@
         <xdr:cNvPr id="387" name="CuadroTexto 386">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{868531C5-7CFC-4BFD-9745-A30B2D199BB9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000083010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21837,7 +21844,7 @@
         <xdr:cNvPr id="388" name="CuadroTexto 387">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C9A975DC-E577-468E-B791-D92EA0A7C22C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000084010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21892,7 +21899,7 @@
         <xdr:cNvPr id="389" name="CuadroTexto 388">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E85028FC-C066-407A-A9CA-617CAACBD592}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000085010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -21947,7 +21954,7 @@
         <xdr:cNvPr id="390" name="CuadroTexto 389">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D35DE71D-3A0C-4934-9A7F-8E95D268A3E6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000086010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -22002,7 +22009,7 @@
         <xdr:cNvPr id="391" name="CuadroTexto 390">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E25F6EE1-DB29-472A-911B-425BDAE8F999}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000087010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -22057,7 +22064,7 @@
         <xdr:cNvPr id="392" name="CuadroTexto 391">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{DCC66F88-76CD-4D40-83F1-40876A4B75EC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000088010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -22112,7 +22119,7 @@
         <xdr:cNvPr id="393" name="CuadroTexto 392">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2FA5E455-4F77-4FD5-B8C1-8D79C3285A2E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000089010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -22167,7 +22174,7 @@
         <xdr:cNvPr id="394" name="CuadroTexto 393">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E22C7FD0-7AAD-4EAD-A0FC-DAFB34392E25}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008A010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -22222,7 +22229,7 @@
         <xdr:cNvPr id="395" name="CuadroTexto 394">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6ED5C0E6-2818-48E4-91D1-FE29F079AFA6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008B010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -22277,7 +22284,7 @@
         <xdr:cNvPr id="396" name="CuadroTexto 395">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{27D86713-7948-42F7-8B6F-D9A8009B6960}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008C010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -22332,7 +22339,7 @@
         <xdr:cNvPr id="397" name="CuadroTexto 396">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E25F6EE1-DB29-472A-911B-425BDAE8F999}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008D010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -22387,7 +22394,7 @@
         <xdr:cNvPr id="398" name="CuadroTexto 397">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{DCC66F88-76CD-4D40-83F1-40876A4B75EC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008E010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -22442,7 +22449,7 @@
         <xdr:cNvPr id="399" name="CuadroTexto 398">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2FA5E455-4F77-4FD5-B8C1-8D79C3285A2E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00008F010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -22899,23 +22906,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K500"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.9375" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.921875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="16.234375" customWidth="1"/>
-    <col min="3" max="3" width="8.46875" customWidth="1"/>
-    <col min="4" max="4" width="6.87890625" style="26" customWidth="1"/>
-    <col min="5" max="5" width="12.703125" customWidth="1"/>
-    <col min="6" max="6" width="14.87890625" customWidth="1"/>
-    <col min="7" max="7" width="33.9375" customWidth="1"/>
-    <col min="8" max="8" width="10.17578125" customWidth="1"/>
-    <col min="9" max="9" width="63.5859375" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="8.05859375" customWidth="1"/>
+    <col min="2" max="2" width="16.23046875" customWidth="1"/>
+    <col min="3" max="3" width="8.4609375" customWidth="1"/>
+    <col min="4" max="4" width="6.84375" style="25" customWidth="1"/>
+    <col min="5" max="5" width="12.69140625" customWidth="1"/>
+    <col min="6" max="6" width="14.84375" customWidth="1"/>
+    <col min="7" max="7" width="33.921875" customWidth="1"/>
+    <col min="8" max="8" width="10.15234375" customWidth="1"/>
+    <col min="9" max="9" width="63.61328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="8.07421875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -22925,7 +22932,7 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="30" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -22950,7 +22957,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:11" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>101</v>
       </c>
@@ -22960,7 +22967,7 @@
       <c r="C2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="32">
+      <c r="D2" s="31">
         <v>46113</v>
       </c>
       <c r="E2" s="5" t="s">
@@ -22981,7 +22988,7 @@
       <c r="J2" s="8"/>
       <c r="K2" s="9"/>
     </row>
-    <row r="3" spans="1:11" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:11" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
         <v>101</v>
       </c>
@@ -22991,7 +22998,7 @@
       <c r="C3" s="4">
         <v>300011807</v>
       </c>
-      <c r="D3" s="32">
+      <c r="D3" s="31">
         <v>46115</v>
       </c>
       <c r="E3" s="5" t="s">
@@ -23012,7 +23019,7 @@
       <c r="J3" s="8"/>
       <c r="K3" s="9"/>
     </row>
-    <row r="4" spans="1:11" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:11" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>40</v>
       </c>
@@ -23022,7 +23029,7 @@
       <c r="C4" s="4">
         <v>26799</v>
       </c>
-      <c r="D4" s="32">
+      <c r="D4" s="31">
         <v>46116</v>
       </c>
       <c r="E4" s="5" t="s">
@@ -23043,7 +23050,7 @@
       <c r="J4" s="8"/>
       <c r="K4" s="9"/>
     </row>
-    <row r="5" spans="1:11" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:11" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
         <v>40</v>
       </c>
@@ -23053,7 +23060,7 @@
       <c r="C5" s="4">
         <v>9559</v>
       </c>
-      <c r="D5" s="32">
+      <c r="D5" s="31">
         <v>46119</v>
       </c>
       <c r="E5" s="5" t="s">
@@ -23074,7 +23081,7 @@
       <c r="J5" s="8"/>
       <c r="K5" s="9"/>
     </row>
-    <row r="6" spans="1:11" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:11" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A6" s="10" t="s">
         <v>101</v>
       </c>
@@ -23084,7 +23091,7 @@
       <c r="C6" s="12">
         <v>6073</v>
       </c>
-      <c r="D6" s="33">
+      <c r="D6" s="32">
         <v>46118</v>
       </c>
       <c r="E6" s="13" t="s">
@@ -23109,7 +23116,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:11" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A7" s="11" t="s">
         <v>101</v>
       </c>
@@ -23119,7 +23126,7 @@
       <c r="C7" s="12">
         <v>422</v>
       </c>
-      <c r="D7" s="33">
+      <c r="D7" s="32">
         <v>46120</v>
       </c>
       <c r="E7" s="13" t="s">
@@ -23140,7 +23147,7 @@
       <c r="J7" s="15"/>
       <c r="K7" s="9"/>
     </row>
-    <row r="8" spans="1:11" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:11" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A8" s="11" t="s">
         <v>101</v>
       </c>
@@ -23150,7 +23157,7 @@
       <c r="C8" s="12">
         <v>6003896</v>
       </c>
-      <c r="D8" s="33">
+      <c r="D8" s="32">
         <v>46120</v>
       </c>
       <c r="E8" s="13" t="s">
@@ -23171,7 +23178,7 @@
       <c r="J8" s="15"/>
       <c r="K8" s="9"/>
     </row>
-    <row r="9" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="10" t="s">
         <v>101</v>
       </c>
@@ -23181,7 +23188,7 @@
       <c r="C9" s="12">
         <v>3822</v>
       </c>
-      <c r="D9" s="33">
+      <c r="D9" s="32">
         <v>46122</v>
       </c>
       <c r="E9" s="13" t="s">
@@ -23202,7 +23209,7 @@
       <c r="J9" s="15"/>
       <c r="K9" s="9"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A10" s="11" t="s">
         <v>101</v>
       </c>
@@ -23212,7 +23219,7 @@
       <c r="C10" s="12">
         <v>3855</v>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="32">
         <v>46125</v>
       </c>
       <c r="E10" s="13" t="s">
@@ -23233,7 +23240,7 @@
       <c r="J10" s="15"/>
       <c r="K10" s="9"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A11" s="16" t="s">
         <v>101</v>
       </c>
@@ -23243,7 +23250,7 @@
       <c r="C11" s="17">
         <v>28319</v>
       </c>
-      <c r="D11" s="34">
+      <c r="D11" s="33">
         <v>46125</v>
       </c>
       <c r="E11" s="16" t="s">
@@ -23264,7 +23271,7 @@
       <c r="J11" s="19"/>
       <c r="K11" s="9"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A12" s="16" t="s">
         <v>101</v>
       </c>
@@ -23274,7 +23281,7 @@
       <c r="C12" s="17">
         <v>114156072</v>
       </c>
-      <c r="D12" s="34">
+      <c r="D12" s="33">
         <v>46125</v>
       </c>
       <c r="E12" s="16" t="s">
@@ -23295,7 +23302,7 @@
       <c r="J12" s="19"/>
       <c r="K12" s="9"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A13" s="16" t="s">
         <v>101</v>
       </c>
@@ -23305,7 +23312,7 @@
       <c r="C13" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="D13" s="34">
+      <c r="D13" s="33">
         <v>46126</v>
       </c>
       <c r="E13" s="16" t="s">
@@ -23326,7 +23333,7 @@
       <c r="J13" s="19"/>
       <c r="K13" s="9"/>
     </row>
-    <row r="14" spans="1:11" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A14" s="16" t="s">
         <v>101</v>
       </c>
@@ -23336,7 +23343,7 @@
       <c r="C14" s="17">
         <v>3500231148</v>
       </c>
-      <c r="D14" s="34">
+      <c r="D14" s="33">
         <v>46126</v>
       </c>
       <c r="E14" s="16" t="s">
@@ -23357,7 +23364,7 @@
       <c r="J14" s="19"/>
       <c r="K14" s="9"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A15" s="16" t="s">
         <v>40</v>
       </c>
@@ -23367,7 +23374,7 @@
       <c r="C15" s="17">
         <v>6178</v>
       </c>
-      <c r="D15" s="34">
+      <c r="D15" s="33">
         <v>46126</v>
       </c>
       <c r="E15" s="16" t="s">
@@ -23388,7 +23395,7 @@
       <c r="J15" s="19"/>
       <c r="K15" s="9"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A16" s="16" t="s">
         <v>40</v>
       </c>
@@ -23398,7 +23405,7 @@
       <c r="C16" s="17">
         <v>21685</v>
       </c>
-      <c r="D16" s="34">
+      <c r="D16" s="33">
         <v>46127</v>
       </c>
       <c r="E16" s="16" t="s">
@@ -23419,7 +23426,7 @@
       <c r="J16" s="19"/>
       <c r="K16" s="9"/>
     </row>
-    <row r="17" spans="1:11" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:11" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A17" s="16" t="s">
         <v>40</v>
       </c>
@@ -23429,7 +23436,7 @@
       <c r="C17" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="D17" s="34">
+      <c r="D17" s="33">
         <v>46127</v>
       </c>
       <c r="E17" s="16" t="s">
@@ -23450,7 +23457,7 @@
       <c r="J17" s="19"/>
       <c r="K17" s="9"/>
     </row>
-    <row r="18" spans="1:11" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:11" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A18" s="16" t="s">
         <v>40</v>
       </c>
@@ -23460,7 +23467,7 @@
       <c r="C18" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="D18" s="34">
+      <c r="D18" s="33">
         <v>46127</v>
       </c>
       <c r="E18" s="16" t="s">
@@ -23481,7 +23488,7 @@
       <c r="J18" s="19"/>
       <c r="K18" s="9"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A19" s="16" t="s">
         <v>40</v>
       </c>
@@ -23491,7 +23498,7 @@
       <c r="C19" s="17">
         <v>741</v>
       </c>
-      <c r="D19" s="34">
+      <c r="D19" s="33">
         <v>46128</v>
       </c>
       <c r="E19" s="16" t="s">
@@ -23512,7 +23519,7 @@
       <c r="J19" s="19"/>
       <c r="K19" s="9"/>
     </row>
-    <row r="20" spans="1:11" ht="15.35" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:11" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A20" s="16" t="s">
         <v>40</v>
       </c>
@@ -23522,7 +23529,7 @@
       <c r="C20" s="17">
         <v>13440</v>
       </c>
-      <c r="D20" s="34">
+      <c r="D20" s="33">
         <v>46129</v>
       </c>
       <c r="E20" s="16" t="s">
@@ -23543,7 +23550,7 @@
       <c r="J20" s="19"/>
       <c r="K20" s="9"/>
     </row>
-    <row r="21" spans="1:11" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:11" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A21" s="18" t="s">
         <v>101</v>
       </c>
@@ -23553,7 +23560,7 @@
       <c r="C21" s="21">
         <v>13462</v>
       </c>
-      <c r="D21" s="35">
+      <c r="D21" s="34">
         <v>46132</v>
       </c>
       <c r="E21" s="18" t="s">
@@ -23571,12 +23578,12 @@
       <c r="I21" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="J21" s="22">
+      <c r="J21" s="37">
         <v>26.52</v>
       </c>
       <c r="K21" s="9"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A22" s="16" t="s">
         <v>101</v>
       </c>
@@ -23586,7 +23593,7 @@
       <c r="C22" s="17">
         <v>8572</v>
       </c>
-      <c r="D22" s="34">
+      <c r="D22" s="33">
         <v>46133</v>
       </c>
       <c r="E22" s="16" t="s">
@@ -23607,7 +23614,7 @@
       <c r="J22" s="19"/>
       <c r="K22" s="9"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A23" s="16" t="s">
         <v>40</v>
       </c>
@@ -23617,7 +23624,7 @@
       <c r="C23" s="17">
         <v>7242083259</v>
       </c>
-      <c r="D23" s="34">
+      <c r="D23" s="33">
         <v>46133</v>
       </c>
       <c r="E23" s="16" t="s">
@@ -23638,7 +23645,7 @@
       <c r="J23" s="19"/>
       <c r="K23" s="9"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A24" s="16" t="s">
         <v>40</v>
       </c>
@@ -23648,7 +23655,7 @@
       <c r="C24" s="17">
         <v>106514</v>
       </c>
-      <c r="D24" s="34">
+      <c r="D24" s="33">
         <v>46133</v>
       </c>
       <c r="E24" s="16" t="s">
@@ -23669,7 +23676,7 @@
       <c r="J24" s="19"/>
       <c r="K24" s="9"/>
     </row>
-    <row r="25" spans="1:11" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:11" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A25" s="16" t="s">
         <v>40</v>
       </c>
@@ -23679,7 +23686,7 @@
       <c r="C25" s="17">
         <v>118308</v>
       </c>
-      <c r="D25" s="34">
+      <c r="D25" s="33">
         <v>46134</v>
       </c>
       <c r="E25" s="16" t="s">
@@ -23700,7 +23707,7 @@
       <c r="J25" s="19"/>
       <c r="K25" s="9"/>
     </row>
-    <row r="26" spans="1:11" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:11" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A26" s="16" t="s">
         <v>101</v>
       </c>
@@ -23710,7 +23717,7 @@
       <c r="C26" s="17">
         <v>13484</v>
       </c>
-      <c r="D26" s="34">
+      <c r="D26" s="33">
         <v>46135</v>
       </c>
       <c r="E26" s="16" t="s">
@@ -23728,14 +23735,14 @@
       <c r="I26" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="J26" s="23">
+      <c r="J26" s="22">
         <v>0.61</v>
       </c>
       <c r="K26" s="9" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A27" s="16" t="s">
         <v>101</v>
       </c>
@@ -23745,7 +23752,7 @@
       <c r="C27" s="17">
         <v>201247337</v>
       </c>
-      <c r="D27" s="34">
+      <c r="D27" s="33">
         <v>46136</v>
       </c>
       <c r="E27" s="16" t="s">
@@ -23766,7 +23773,7 @@
       <c r="J27" s="19"/>
       <c r="K27" s="9"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A28" s="16" t="s">
         <v>101</v>
       </c>
@@ -23776,7 +23783,7 @@
       <c r="C28" s="17">
         <v>201247336</v>
       </c>
-      <c r="D28" s="34">
+      <c r="D28" s="33">
         <v>46136</v>
       </c>
       <c r="E28" s="16" t="s">
@@ -23797,7 +23804,7 @@
       <c r="J28" s="19"/>
       <c r="K28" s="9"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A29" s="16" t="s">
         <v>101</v>
       </c>
@@ -23807,7 +23814,7 @@
       <c r="C29" s="17">
         <v>201247338</v>
       </c>
-      <c r="D29" s="34">
+      <c r="D29" s="33">
         <v>46136</v>
       </c>
       <c r="E29" s="16" t="s">
@@ -23828,7 +23835,7 @@
       <c r="J29" s="19"/>
       <c r="K29" s="9"/>
     </row>
-    <row r="30" spans="1:11" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A30" s="16" t="s">
         <v>40</v>
       </c>
@@ -23838,7 +23845,7 @@
       <c r="C30" s="17">
         <v>540</v>
       </c>
-      <c r="D30" s="34">
+      <c r="D30" s="33">
         <v>46136</v>
       </c>
       <c r="E30" s="16" t="s">
@@ -23856,30 +23863,30 @@
       <c r="I30" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="J30" s="23">
+      <c r="J30" s="22">
         <v>2</v>
       </c>
       <c r="K30" s="9" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.5">
-      <c r="A31" s="24" t="s">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A31" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="24" t="s">
+      <c r="B31" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="C31" s="25">
+      <c r="C31" s="24">
         <v>1851984</v>
       </c>
-      <c r="D31" s="26">
+      <c r="D31" s="25">
         <v>46137</v>
       </c>
-      <c r="E31" s="24" t="s">
+      <c r="E31" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="F31" s="24" t="s">
+      <c r="F31" s="23" t="s">
         <v>43</v>
       </c>
       <c r="G31" t="s">
@@ -23889,59 +23896,59 @@
         <f>IF(G31="","",VLOOKUP(G31,[1]REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO C</v>
       </c>
-      <c r="I31" s="27" t="s">
+      <c r="I31" s="26" t="s">
         <v>90</v>
       </c>
       <c r="K31" s="9"/>
     </row>
-    <row r="32" spans="1:11" ht="28.7" x14ac:dyDescent="0.5">
-      <c r="A32" s="24" t="s">
+    <row r="32" spans="1:11" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A32" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="B32" s="24" t="s">
+      <c r="B32" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="25">
+      <c r="C32" s="24">
         <v>1818</v>
       </c>
-      <c r="D32" s="26">
+      <c r="D32" s="25">
         <v>46139</v>
       </c>
-      <c r="E32" s="24" t="s">
+      <c r="E32" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="F32" s="24" t="s">
+      <c r="F32" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="G32" s="28" t="s">
+      <c r="G32" s="27" t="s">
         <v>23</v>
       </c>
       <c r="H32" t="str">
         <f>IF(G32="","",VLOOKUP(G32,[1]REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO C</v>
       </c>
-      <c r="I32" s="27" t="s">
+      <c r="I32" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="K32" s="29"/>
-    </row>
-    <row r="33" spans="1:11" ht="28.7" x14ac:dyDescent="0.5">
-      <c r="A33" s="24" t="s">
+      <c r="K32" s="28"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A33" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="24" t="s">
+      <c r="B33" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="C33" s="25">
+      <c r="C33" s="24">
         <v>610211463</v>
       </c>
-      <c r="D33" s="26">
+      <c r="D33" s="25">
         <v>46139</v>
       </c>
-      <c r="E33" s="24" t="s">
+      <c r="E33" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="F33" s="24" t="s">
+      <c r="F33" s="23" t="s">
         <v>84</v>
       </c>
       <c r="G33" t="s">
@@ -23951,64 +23958,64 @@
         <f>IF(G33="","",VLOOKUP(G33,[1]REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO A</v>
       </c>
-      <c r="I33" s="27" t="s">
+      <c r="I33" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="K33" s="29"/>
-    </row>
-    <row r="34" spans="1:11" ht="28.7" x14ac:dyDescent="0.5">
-      <c r="A34" s="24" t="s">
+      <c r="K33" s="28"/>
+    </row>
+    <row r="34" spans="1:11" ht="43.75" x14ac:dyDescent="0.4">
+      <c r="A34" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="B34" s="24" t="s">
+      <c r="B34" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="C34" s="25">
+      <c r="C34" s="24">
         <v>30861</v>
       </c>
-      <c r="D34" s="26">
+      <c r="D34" s="25">
         <v>46139</v>
       </c>
-      <c r="E34" s="24" t="s">
+      <c r="E34" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="F34" s="24" t="s">
+      <c r="F34" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="G34" s="28" t="s">
+      <c r="G34" s="27" t="s">
         <v>24</v>
       </c>
       <c r="H34" t="str">
         <f>IF(G34="","",VLOOKUP(G34,[1]REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO C</v>
       </c>
-      <c r="I34" s="30" t="s">
+      <c r="I34" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="J34" s="37">
+      <c r="J34" s="36">
         <v>1.62</v>
       </c>
-      <c r="K34" s="29" t="s">
+      <c r="K34" s="28" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.5">
-      <c r="A35" s="24" t="s">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A35" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="B35" s="24" t="s">
+      <c r="B35" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="C35" s="25">
+      <c r="C35" s="24">
         <v>13545</v>
       </c>
-      <c r="D35" s="26">
+      <c r="D35" s="25">
         <v>46141</v>
       </c>
-      <c r="E35" s="24" t="s">
+      <c r="E35" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="F35" s="24" t="s">
+      <c r="F35" s="23" t="s">
         <v>84</v>
       </c>
       <c r="G35" t="s">
@@ -24018,27 +24025,27 @@
         <f>IF(G35="","",VLOOKUP(G35,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v>TIPO C</v>
       </c>
-      <c r="I35" s="36" t="s">
+      <c r="I35" s="35" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.5">
-      <c r="A36" s="24" t="s">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A36" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="B36" s="24" t="s">
+      <c r="B36" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="C36" s="25">
+      <c r="C36" s="24">
         <v>53076</v>
       </c>
-      <c r="D36" s="26">
+      <c r="D36" s="25">
         <v>46142</v>
       </c>
-      <c r="E36" s="24" t="s">
+      <c r="E36" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="F36" s="24" t="s">
+      <c r="F36" s="23" t="s">
         <v>34</v>
       </c>
       <c r="G36" t="s">
@@ -24048,27 +24055,27 @@
         <f>IF(G36="","",VLOOKUP(G36,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v>TIPO B</v>
       </c>
-      <c r="I36" s="36" t="s">
+      <c r="I36" s="35" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.5">
-      <c r="A37" s="24" t="s">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A37" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="B37" s="24" t="s">
+      <c r="B37" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="C37" s="25">
+      <c r="C37" s="24">
         <v>1853893</v>
       </c>
-      <c r="D37" s="26">
+      <c r="D37" s="25">
         <v>46142</v>
       </c>
-      <c r="E37" s="24" t="s">
+      <c r="E37" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="F37" s="24" t="s">
+      <c r="F37" s="23" t="s">
         <v>87</v>
       </c>
       <c r="G37" t="s">
@@ -24078,27 +24085,27 @@
         <f>IF(G37="","",VLOOKUP(G37,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v>TIPO C</v>
       </c>
-      <c r="I37" s="36" t="s">
+      <c r="I37" s="35" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.5">
-      <c r="A38" s="24" t="s">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A38" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="B38" s="24" t="s">
+      <c r="B38" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="C38" s="25">
+      <c r="C38" s="24">
         <v>1853894</v>
       </c>
-      <c r="D38" s="26">
+      <c r="D38" s="25">
         <v>46142</v>
       </c>
-      <c r="E38" s="24" t="s">
+      <c r="E38" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="F38" s="24" t="s">
+      <c r="F38" s="23" t="s">
         <v>87</v>
       </c>
       <c r="G38" t="s">
@@ -24108,27 +24115,27 @@
         <f>IF(G38="","",VLOOKUP(G38,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v>TIPO C</v>
       </c>
-      <c r="I38" s="36" t="s">
+      <c r="I38" s="35" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.5">
-      <c r="A39" s="24" t="s">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A39" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="B39" s="24" t="s">
+      <c r="B39" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="C39" s="25">
+      <c r="C39" s="24">
         <v>6433</v>
       </c>
-      <c r="D39" s="26">
+      <c r="D39" s="25">
         <v>46142</v>
       </c>
-      <c r="E39" s="24" t="s">
+      <c r="E39" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="F39" s="24" t="s">
+      <c r="F39" s="23" t="s">
         <v>87</v>
       </c>
       <c r="G39" t="s">
@@ -24138,2771 +24145,2771 @@
         <f>IF(G39="","",VLOOKUP(G39,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v>TIPO B</v>
       </c>
-      <c r="I39" s="36" t="s">
+      <c r="I39" s="35" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.4">
       <c r="H40" t="str">
         <f>IF(G40="","",VLOOKUP(G40,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.4">
       <c r="H41" t="str">
         <f>IF(G41="","",VLOOKUP(G41,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.4">
       <c r="H42" t="str">
         <f>IF(G42="","",VLOOKUP(G42,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.4">
       <c r="H43" t="str">
         <f>IF(G43="","",VLOOKUP(G43,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.4">
       <c r="H44" t="str">
         <f>IF(G44="","",VLOOKUP(G44,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.4">
       <c r="H45" t="str">
         <f>IF(G45="","",VLOOKUP(G45,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.4">
       <c r="H46" t="str">
         <f>IF(G46="","",VLOOKUP(G46,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.4">
       <c r="H47" t="str">
         <f>IF(G47="","",VLOOKUP(G47,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.4">
       <c r="H48" t="str">
         <f>IF(G48="","",VLOOKUP(G48,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="49" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="49" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H49" t="str">
         <f>IF(G49="","",VLOOKUP(G49,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="50" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="50" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H50" t="str">
         <f>IF(G50="","",VLOOKUP(G50,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="51" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="51" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H51" t="str">
         <f>IF(G51="","",VLOOKUP(G51,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="52" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="52" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H52" t="str">
         <f>IF(G52="","",VLOOKUP(G52,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="53" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="53" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H53" t="str">
         <f>IF(G53="","",VLOOKUP(G53,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="54" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="54" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H54" t="str">
         <f>IF(G54="","",VLOOKUP(G54,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="55" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="55" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H55" t="str">
         <f>IF(G55="","",VLOOKUP(G55,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="56" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="56" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H56" t="str">
         <f>IF(G56="","",VLOOKUP(G56,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="57" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="57" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H57" t="str">
         <f>IF(G57="","",VLOOKUP(G57,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="58" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="58" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H58" t="str">
         <f>IF(G58="","",VLOOKUP(G58,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="59" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="59" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H59" t="str">
         <f>IF(G59="","",VLOOKUP(G59,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="60" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="60" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H60" t="str">
         <f>IF(G60="","",VLOOKUP(G60,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="61" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="61" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H61" t="str">
         <f>IF(G61="","",VLOOKUP(G61,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="62" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="62" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H62" t="str">
         <f>IF(G62="","",VLOOKUP(G62,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="63" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="63" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H63" t="str">
         <f>IF(G63="","",VLOOKUP(G63,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="64" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="64" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H64" t="str">
         <f>IF(G64="","",VLOOKUP(G64,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="65" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="65" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H65" t="str">
         <f>IF(G65="","",VLOOKUP(G65,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="66" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="66" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H66" t="str">
         <f>IF(G66="","",VLOOKUP(G66,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="67" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="67" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H67" t="str">
         <f>IF(G67="","",VLOOKUP(G67,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="68" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="68" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H68" t="str">
         <f>IF(G68="","",VLOOKUP(G68,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="69" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="69" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H69" t="str">
         <f>IF(G69="","",VLOOKUP(G69,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="70" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="70" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H70" t="str">
         <f>IF(G70="","",VLOOKUP(G70,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="71" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="71" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H71" t="str">
         <f>IF(G71="","",VLOOKUP(G71,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="72" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="72" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H72" t="str">
         <f>IF(G72="","",VLOOKUP(G72,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="73" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="73" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H73" t="str">
         <f>IF(G73="","",VLOOKUP(G73,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="74" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="74" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H74" t="str">
         <f>IF(G74="","",VLOOKUP(G74,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="75" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="75" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H75" t="str">
         <f>IF(G75="","",VLOOKUP(G75,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="76" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="76" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H76" t="str">
         <f>IF(G76="","",VLOOKUP(G76,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="77" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="77" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H77" t="str">
         <f>IF(G77="","",VLOOKUP(G77,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="78" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="78" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H78" t="str">
         <f>IF(G78="","",VLOOKUP(G78,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="79" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="79" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H79" t="str">
         <f>IF(G79="","",VLOOKUP(G79,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="80" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="80" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H80" t="str">
         <f>IF(G80="","",VLOOKUP(G80,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="81" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="81" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H81" t="str">
         <f>IF(G81="","",VLOOKUP(G81,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="82" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="82" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H82" t="str">
         <f>IF(G82="","",VLOOKUP(G82,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="83" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="83" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H83" t="str">
         <f>IF(G83="","",VLOOKUP(G83,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="84" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="84" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H84" t="str">
         <f>IF(G84="","",VLOOKUP(G84,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="85" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="85" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H85" t="str">
         <f>IF(G85="","",VLOOKUP(G85,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="86" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="86" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H86" t="str">
         <f>IF(G86="","",VLOOKUP(G86,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="87" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="87" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H87" t="str">
         <f>IF(G87="","",VLOOKUP(G87,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="88" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="88" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H88" t="str">
         <f>IF(G88="","",VLOOKUP(G88,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="89" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="89" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H89" t="str">
         <f>IF(G89="","",VLOOKUP(G89,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="90" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="90" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H90" t="str">
         <f>IF(G90="","",VLOOKUP(G90,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="91" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="91" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H91" t="str">
         <f>IF(G91="","",VLOOKUP(G91,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="92" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="92" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H92" t="str">
         <f>IF(G92="","",VLOOKUP(G92,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="93" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="93" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H93" t="str">
         <f>IF(G93="","",VLOOKUP(G93,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="94" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="94" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H94" t="str">
         <f>IF(G94="","",VLOOKUP(G94,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="95" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="95" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H95" t="str">
         <f>IF(G95="","",VLOOKUP(G95,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="96" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="96" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H96" t="str">
         <f>IF(G96="","",VLOOKUP(G96,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="97" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="97" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H97" t="str">
         <f>IF(G97="","",VLOOKUP(G97,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="98" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="98" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H98" t="str">
         <f>IF(G98="","",VLOOKUP(G98,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="99" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="99" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H99" t="str">
         <f>IF(G99="","",VLOOKUP(G99,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="100" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="100" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H100" t="str">
         <f>IF(G100="","",VLOOKUP(G100,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="101" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="101" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H101" t="str">
         <f>IF(G101="","",VLOOKUP(G101,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="102" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="102" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H102" t="str">
         <f>IF(G102="","",VLOOKUP(G102,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="103" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="103" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H103" t="str">
         <f>IF(G103="","",VLOOKUP(G103,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="104" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="104" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H104" t="str">
         <f>IF(G104="","",VLOOKUP(G104,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="105" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="105" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H105" t="str">
         <f>IF(G105="","",VLOOKUP(G105,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="106" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="106" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H106" t="str">
         <f>IF(G106="","",VLOOKUP(G106,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="107" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="107" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H107" t="str">
         <f>IF(G107="","",VLOOKUP(G107,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="108" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="108" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H108" t="str">
         <f>IF(G108="","",VLOOKUP(G108,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="109" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="109" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H109" t="str">
         <f>IF(G109="","",VLOOKUP(G109,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="110" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="110" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H110" t="str">
         <f>IF(G110="","",VLOOKUP(G110,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="111" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="111" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H111" t="str">
         <f>IF(G111="","",VLOOKUP(G111,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="112" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="112" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H112" t="str">
         <f>IF(G112="","",VLOOKUP(G112,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="113" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="113" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H113" t="str">
         <f>IF(G113="","",VLOOKUP(G113,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="114" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="114" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H114" t="str">
         <f>IF(G114="","",VLOOKUP(G114,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="115" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="115" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H115" t="str">
         <f>IF(G115="","",VLOOKUP(G115,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="116" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="116" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H116" t="str">
         <f>IF(G116="","",VLOOKUP(G116,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="117" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="117" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H117" t="str">
         <f>IF(G117="","",VLOOKUP(G117,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="118" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="118" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H118" t="str">
         <f>IF(G118="","",VLOOKUP(G118,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="119" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="119" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H119" t="str">
         <f>IF(G119="","",VLOOKUP(G119,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="120" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="120" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H120" t="str">
         <f>IF(G120="","",VLOOKUP(G120,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="121" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="121" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H121" t="str">
         <f>IF(G121="","",VLOOKUP(G121,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="122" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="122" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H122" t="str">
         <f>IF(G122="","",VLOOKUP(G122,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="123" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="123" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H123" t="str">
         <f>IF(G123="","",VLOOKUP(G123,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="124" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="124" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H124" t="str">
         <f>IF(G124="","",VLOOKUP(G124,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="125" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="125" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H125" t="str">
         <f>IF(G125="","",VLOOKUP(G125,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="126" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H126" t="str">
         <f>IF(G126="","",VLOOKUP(G126,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="127" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H127" t="str">
         <f>IF(G127="","",VLOOKUP(G127,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="128" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="128" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H128" t="str">
         <f>IF(G128="","",VLOOKUP(G128,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="129" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="129" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H129" t="str">
         <f>IF(G129="","",VLOOKUP(G129,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="130" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="130" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H130" t="str">
         <f>IF(G130="","",VLOOKUP(G130,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="131" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="131" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H131" t="str">
         <f>IF(G131="","",VLOOKUP(G131,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="132" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="132" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H132" t="str">
         <f>IF(G132="","",VLOOKUP(G132,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="133" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="133" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H133" t="str">
         <f>IF(G133="","",VLOOKUP(G133,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="134" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="134" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H134" t="str">
         <f>IF(G134="","",VLOOKUP(G134,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="135" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="135" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H135" t="str">
         <f>IF(G135="","",VLOOKUP(G135,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="136" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="136" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H136" t="str">
         <f>IF(G136="","",VLOOKUP(G136,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="137" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="137" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H137" t="str">
         <f>IF(G137="","",VLOOKUP(G137,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="138" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="138" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H138" t="str">
         <f>IF(G138="","",VLOOKUP(G138,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="139" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="139" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H139" t="str">
         <f>IF(G139="","",VLOOKUP(G139,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="140" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="140" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H140" t="str">
         <f>IF(G140="","",VLOOKUP(G140,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="141" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="141" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H141" t="str">
         <f>IF(G141="","",VLOOKUP(G141,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="142" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="142" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H142" t="str">
         <f>IF(G142="","",VLOOKUP(G142,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="143" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="143" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H143" t="str">
         <f>IF(G143="","",VLOOKUP(G143,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="144" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="144" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H144" t="str">
         <f>IF(G144="","",VLOOKUP(G144,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="145" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="145" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H145" t="str">
         <f>IF(G145="","",VLOOKUP(G145,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="146" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="146" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H146" t="str">
         <f>IF(G146="","",VLOOKUP(G146,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="147" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="147" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H147" t="str">
         <f>IF(G147="","",VLOOKUP(G147,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="148" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="148" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H148" t="str">
         <f>IF(G148="","",VLOOKUP(G148,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="149" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="149" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H149" t="str">
         <f>IF(G149="","",VLOOKUP(G149,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="150" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="150" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H150" t="str">
         <f>IF(G150="","",VLOOKUP(G150,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="151" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="151" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H151" t="str">
         <f>IF(G151="","",VLOOKUP(G151,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="152" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="152" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H152" t="str">
         <f>IF(G152="","",VLOOKUP(G152,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="153" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="153" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H153" t="str">
         <f>IF(G153="","",VLOOKUP(G153,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="154" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="154" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H154" t="str">
         <f>IF(G154="","",VLOOKUP(G154,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="155" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="155" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H155" t="str">
         <f>IF(G155="","",VLOOKUP(G155,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="156" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="156" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H156" t="str">
         <f>IF(G156="","",VLOOKUP(G156,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="157" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="157" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H157" t="str">
         <f>IF(G157="","",VLOOKUP(G157,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="158" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="158" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H158" t="str">
         <f>IF(G158="","",VLOOKUP(G158,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="159" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="159" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H159" t="str">
         <f>IF(G159="","",VLOOKUP(G159,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="160" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="160" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H160" t="str">
         <f>IF(G160="","",VLOOKUP(G160,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="161" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="161" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H161" t="str">
         <f>IF(G161="","",VLOOKUP(G161,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="162" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="162" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H162" t="str">
         <f>IF(G162="","",VLOOKUP(G162,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="163" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="163" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H163" t="str">
         <f>IF(G163="","",VLOOKUP(G163,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="164" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="164" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H164" t="str">
         <f>IF(G164="","",VLOOKUP(G164,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="165" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="165" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H165" t="str">
         <f>IF(G165="","",VLOOKUP(G165,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="166" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="166" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H166" t="str">
         <f>IF(G166="","",VLOOKUP(G166,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="167" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="167" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H167" t="str">
         <f>IF(G167="","",VLOOKUP(G167,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="168" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="168" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H168" t="str">
         <f>IF(G168="","",VLOOKUP(G168,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="169" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="169" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H169" t="str">
         <f>IF(G169="","",VLOOKUP(G169,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="170" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="170" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H170" t="str">
         <f>IF(G170="","",VLOOKUP(G170,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="171" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="171" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H171" t="str">
         <f>IF(G171="","",VLOOKUP(G171,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="172" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="172" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H172" t="str">
         <f>IF(G172="","",VLOOKUP(G172,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="173" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="173" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H173" t="str">
         <f>IF(G173="","",VLOOKUP(G173,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="174" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="174" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H174" t="str">
         <f>IF(G174="","",VLOOKUP(G174,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="175" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="175" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H175" t="str">
         <f>IF(G175="","",VLOOKUP(G175,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="176" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="176" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H176" t="str">
         <f>IF(G176="","",VLOOKUP(G176,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="177" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="177" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H177" t="str">
         <f>IF(G177="","",VLOOKUP(G177,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="178" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="178" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H178" t="str">
         <f>IF(G178="","",VLOOKUP(G178,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="179" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="179" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H179" t="str">
         <f>IF(G179="","",VLOOKUP(G179,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="180" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="180" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H180" t="str">
         <f>IF(G180="","",VLOOKUP(G180,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="181" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="181" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H181" t="str">
         <f>IF(G181="","",VLOOKUP(G181,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="182" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="182" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H182" t="str">
         <f>IF(G182="","",VLOOKUP(G182,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="183" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="183" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H183" t="str">
         <f>IF(G183="","",VLOOKUP(G183,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="184" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="184" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H184" t="str">
         <f>IF(G184="","",VLOOKUP(G184,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="185" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="185" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H185" t="str">
         <f>IF(G185="","",VLOOKUP(G185,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="186" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="186" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H186" t="str">
         <f>IF(G186="","",VLOOKUP(G186,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="187" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="187" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H187" t="str">
         <f>IF(G187="","",VLOOKUP(G187,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="188" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="188" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H188" t="str">
         <f>IF(G188="","",VLOOKUP(G188,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="189" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="189" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H189" t="str">
         <f>IF(G189="","",VLOOKUP(G189,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="190" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="190" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H190" t="str">
         <f>IF(G190="","",VLOOKUP(G190,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="191" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="191" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H191" t="str">
         <f>IF(G191="","",VLOOKUP(G191,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="192" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="192" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H192" t="str">
         <f>IF(G192="","",VLOOKUP(G192,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="193" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="193" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H193" t="str">
         <f>IF(G193="","",VLOOKUP(G193,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="194" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="194" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H194" t="str">
         <f>IF(G194="","",VLOOKUP(G194,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="195" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="195" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H195" t="str">
         <f>IF(G195="","",VLOOKUP(G195,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="196" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="196" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H196" t="str">
         <f>IF(G196="","",VLOOKUP(G196,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="197" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="197" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H197" t="str">
         <f>IF(G197="","",VLOOKUP(G197,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="198" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="198" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H198" t="str">
         <f>IF(G198="","",VLOOKUP(G198,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="199" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="199" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H199" t="str">
         <f>IF(G199="","",VLOOKUP(G199,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="200" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="200" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H200" t="str">
         <f>IF(G200="","",VLOOKUP(G200,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="201" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="201" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H201" t="str">
         <f>IF(G201="","",VLOOKUP(G201,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="202" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="202" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H202" t="str">
         <f>IF(G202="","",VLOOKUP(G202,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="203" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="203" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H203" t="str">
         <f>IF(G203="","",VLOOKUP(G203,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="204" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="204" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H204" t="str">
         <f>IF(G204="","",VLOOKUP(G204,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="205" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="205" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H205" t="str">
         <f>IF(G205="","",VLOOKUP(G205,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="206" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="206" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H206" t="str">
         <f>IF(G206="","",VLOOKUP(G206,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="207" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="207" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H207" t="str">
         <f>IF(G207="","",VLOOKUP(G207,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="208" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="208" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H208" t="str">
         <f>IF(G208="","",VLOOKUP(G208,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="209" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="209" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H209" t="str">
         <f>IF(G209="","",VLOOKUP(G209,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="210" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="210" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H210" t="str">
         <f>IF(G210="","",VLOOKUP(G210,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="211" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="211" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H211" t="str">
         <f>IF(G211="","",VLOOKUP(G211,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="212" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="212" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H212" t="str">
         <f>IF(G212="","",VLOOKUP(G212,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="213" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="213" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H213" t="str">
         <f>IF(G213="","",VLOOKUP(G213,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="214" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="214" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H214" t="str">
         <f>IF(G214="","",VLOOKUP(G214,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="215" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="215" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H215" t="str">
         <f>IF(G215="","",VLOOKUP(G215,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="216" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="216" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H216" t="str">
         <f>IF(G216="","",VLOOKUP(G216,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="217" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="217" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H217" t="str">
         <f>IF(G217="","",VLOOKUP(G217,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="218" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="218" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H218" t="str">
         <f>IF(G218="","",VLOOKUP(G218,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="219" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="219" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H219" t="str">
         <f>IF(G219="","",VLOOKUP(G219,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="220" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="220" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H220" t="str">
         <f>IF(G220="","",VLOOKUP(G220,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="221" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="221" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H221" t="str">
         <f>IF(G221="","",VLOOKUP(G221,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="222" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="222" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H222" t="str">
         <f>IF(G222="","",VLOOKUP(G222,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="223" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="223" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H223" t="str">
         <f>IF(G223="","",VLOOKUP(G223,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="224" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="224" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H224" t="str">
         <f>IF(G224="","",VLOOKUP(G224,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="225" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="225" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H225" t="str">
         <f>IF(G225="","",VLOOKUP(G225,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="226" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="226" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H226" t="str">
         <f>IF(G226="","",VLOOKUP(G226,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="227" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="227" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H227" t="str">
         <f>IF(G227="","",VLOOKUP(G227,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="228" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="228" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H228" t="str">
         <f>IF(G228="","",VLOOKUP(G228,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="229" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="229" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H229" t="str">
         <f>IF(G229="","",VLOOKUP(G229,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="230" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="230" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H230" t="str">
         <f>IF(G230="","",VLOOKUP(G230,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="231" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="231" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H231" t="str">
         <f>IF(G231="","",VLOOKUP(G231,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="232" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="232" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H232" t="str">
         <f>IF(G232="","",VLOOKUP(G232,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="233" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="233" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H233" t="str">
         <f>IF(G233="","",VLOOKUP(G233,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="234" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="234" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H234" t="str">
         <f>IF(G234="","",VLOOKUP(G234,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="235" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="235" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H235" t="str">
         <f>IF(G235="","",VLOOKUP(G235,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="236" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="236" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H236" t="str">
         <f>IF(G236="","",VLOOKUP(G236,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="237" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="237" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H237" t="str">
         <f>IF(G237="","",VLOOKUP(G237,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="238" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="238" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H238" t="str">
         <f>IF(G238="","",VLOOKUP(G238,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="239" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="239" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H239" t="str">
         <f>IF(G239="","",VLOOKUP(G239,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="240" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="240" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H240" t="str">
         <f>IF(G240="","",VLOOKUP(G240,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="241" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="241" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H241" t="str">
         <f>IF(G241="","",VLOOKUP(G241,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="242" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="242" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H242" t="str">
         <f>IF(G242="","",VLOOKUP(G242,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="243" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="243" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H243" t="str">
         <f>IF(G243="","",VLOOKUP(G243,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="244" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="244" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H244" t="str">
         <f>IF(G244="","",VLOOKUP(G244,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="245" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="245" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H245" t="str">
         <f>IF(G245="","",VLOOKUP(G245,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="246" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="246" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H246" t="str">
         <f>IF(G246="","",VLOOKUP(G246,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="247" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="247" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H247" t="str">
         <f>IF(G247="","",VLOOKUP(G247,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="248" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="248" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H248" t="str">
         <f>IF(G248="","",VLOOKUP(G248,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="249" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="249" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H249" t="str">
         <f>IF(G249="","",VLOOKUP(G249,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="250" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="250" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H250" t="str">
         <f>IF(G250="","",VLOOKUP(G250,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="251" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="251" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H251" t="str">
         <f>IF(G251="","",VLOOKUP(G251,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="252" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="252" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H252" t="str">
         <f>IF(G252="","",VLOOKUP(G252,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="253" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="253" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H253" t="str">
         <f>IF(G253="","",VLOOKUP(G253,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="254" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="254" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H254" t="str">
         <f>IF(G254="","",VLOOKUP(G254,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="255" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="255" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H255" t="str">
         <f>IF(G255="","",VLOOKUP(G255,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="256" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="256" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H256" t="str">
         <f>IF(G256="","",VLOOKUP(G256,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="257" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="257" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H257" t="str">
         <f>IF(G257="","",VLOOKUP(G257,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="258" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="258" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H258" t="str">
         <f>IF(G258="","",VLOOKUP(G258,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="259" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="259" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H259" t="str">
         <f>IF(G259="","",VLOOKUP(G259,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="260" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="260" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H260" t="str">
         <f>IF(G260="","",VLOOKUP(G260,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="261" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="261" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H261" t="str">
         <f>IF(G261="","",VLOOKUP(G261,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="262" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="262" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H262" t="str">
         <f>IF(G262="","",VLOOKUP(G262,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="263" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="263" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H263" t="str">
         <f>IF(G263="","",VLOOKUP(G263,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="264" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="264" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H264" t="str">
         <f>IF(G264="","",VLOOKUP(G264,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="265" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="265" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H265" t="str">
         <f>IF(G265="","",VLOOKUP(G265,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="266" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="266" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H266" t="str">
         <f>IF(G266="","",VLOOKUP(G266,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="267" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="267" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H267" t="str">
         <f>IF(G267="","",VLOOKUP(G267,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="268" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="268" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H268" t="str">
         <f>IF(G268="","",VLOOKUP(G268,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="269" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="269" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H269" t="str">
         <f>IF(G269="","",VLOOKUP(G269,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="270" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="270" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H270" t="str">
         <f>IF(G270="","",VLOOKUP(G270,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="271" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="271" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H271" t="str">
         <f>IF(G271="","",VLOOKUP(G271,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="272" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="272" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H272" t="str">
         <f>IF(G272="","",VLOOKUP(G272,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="273" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="273" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H273" t="str">
         <f>IF(G273="","",VLOOKUP(G273,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="274" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="274" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H274" t="str">
         <f>IF(G274="","",VLOOKUP(G274,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="275" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="275" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H275" t="str">
         <f>IF(G275="","",VLOOKUP(G275,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="276" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="276" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H276" t="str">
         <f>IF(G276="","",VLOOKUP(G276,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="277" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="277" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H277" t="str">
         <f>IF(G277="","",VLOOKUP(G277,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="278" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="278" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H278" t="str">
         <f>IF(G278="","",VLOOKUP(G278,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="279" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="279" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H279" t="str">
         <f>IF(G279="","",VLOOKUP(G279,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="280" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="280" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H280" t="str">
         <f>IF(G280="","",VLOOKUP(G280,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="281" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="281" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H281" t="str">
         <f>IF(G281="","",VLOOKUP(G281,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="282" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="282" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H282" t="str">
         <f>IF(G282="","",VLOOKUP(G282,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="283" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="283" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H283" t="str">
         <f>IF(G283="","",VLOOKUP(G283,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="284" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="284" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H284" t="str">
         <f>IF(G284="","",VLOOKUP(G284,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="285" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="285" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H285" t="str">
         <f>IF(G285="","",VLOOKUP(G285,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="286" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="286" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H286" t="str">
         <f>IF(G286="","",VLOOKUP(G286,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="287" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="287" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H287" t="str">
         <f>IF(G287="","",VLOOKUP(G287,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="288" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="288" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H288" t="str">
         <f>IF(G288="","",VLOOKUP(G288,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="289" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="289" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H289" t="str">
         <f>IF(G289="","",VLOOKUP(G289,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="290" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="290" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H290" t="str">
         <f>IF(G290="","",VLOOKUP(G290,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="291" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="291" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H291" t="str">
         <f>IF(G291="","",VLOOKUP(G291,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="292" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="292" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H292" t="str">
         <f>IF(G292="","",VLOOKUP(G292,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="293" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="293" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H293" t="str">
         <f>IF(G293="","",VLOOKUP(G293,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="294" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="294" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H294" t="str">
         <f>IF(G294="","",VLOOKUP(G294,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="295" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="295" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H295" t="str">
         <f>IF(G295="","",VLOOKUP(G295,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="296" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="296" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H296" t="str">
         <f>IF(G296="","",VLOOKUP(G296,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="297" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="297" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H297" t="str">
         <f>IF(G297="","",VLOOKUP(G297,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="298" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="298" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H298" t="str">
         <f>IF(G298="","",VLOOKUP(G298,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="299" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="299" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H299" t="str">
         <f>IF(G299="","",VLOOKUP(G299,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="300" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="300" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H300" t="str">
         <f>IF(G300="","",VLOOKUP(G300,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="301" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="301" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H301" t="str">
         <f>IF(G301="","",VLOOKUP(G301,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="302" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="302" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H302" t="str">
         <f>IF(G302="","",VLOOKUP(G302,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="303" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="303" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H303" t="str">
         <f>IF(G303="","",VLOOKUP(G303,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="304" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="304" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H304" t="str">
         <f>IF(G304="","",VLOOKUP(G304,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="305" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="305" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H305" t="str">
         <f>IF(G305="","",VLOOKUP(G305,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="306" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="306" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H306" t="str">
         <f>IF(G306="","",VLOOKUP(G306,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="307" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="307" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H307" t="str">
         <f>IF(G307="","",VLOOKUP(G307,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="308" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="308" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H308" t="str">
         <f>IF(G308="","",VLOOKUP(G308,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="309" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="309" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H309" t="str">
         <f>IF(G309="","",VLOOKUP(G309,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="310" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="310" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H310" t="str">
         <f>IF(G310="","",VLOOKUP(G310,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="311" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="311" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H311" t="str">
         <f>IF(G311="","",VLOOKUP(G311,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="312" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="312" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H312" t="str">
         <f>IF(G312="","",VLOOKUP(G312,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="313" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="313" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H313" t="str">
         <f>IF(G313="","",VLOOKUP(G313,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="314" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="314" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H314" t="str">
         <f>IF(G314="","",VLOOKUP(G314,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="315" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="315" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H315" t="str">
         <f>IF(G315="","",VLOOKUP(G315,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="316" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="316" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H316" t="str">
         <f>IF(G316="","",VLOOKUP(G316,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="317" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="317" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H317" t="str">
         <f>IF(G317="","",VLOOKUP(G317,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="318" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="318" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H318" t="str">
         <f>IF(G318="","",VLOOKUP(G318,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="319" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="319" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H319" t="str">
         <f>IF(G319="","",VLOOKUP(G319,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="320" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="320" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H320" t="str">
         <f>IF(G320="","",VLOOKUP(G320,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="321" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="321" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H321" t="str">
         <f>IF(G321="","",VLOOKUP(G321,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="322" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="322" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H322" t="str">
         <f>IF(G322="","",VLOOKUP(G322,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="323" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="323" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H323" t="str">
         <f>IF(G323="","",VLOOKUP(G323,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="324" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="324" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H324" t="str">
         <f>IF(G324="","",VLOOKUP(G324,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="325" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="325" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H325" t="str">
         <f>IF(G325="","",VLOOKUP(G325,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="326" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="326" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H326" t="str">
         <f>IF(G326="","",VLOOKUP(G326,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="327" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="327" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H327" t="str">
         <f>IF(G327="","",VLOOKUP(G327,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="328" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="328" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H328" t="str">
         <f>IF(G328="","",VLOOKUP(G328,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="329" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="329" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H329" t="str">
         <f>IF(G329="","",VLOOKUP(G329,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="330" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="330" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H330" t="str">
         <f>IF(G330="","",VLOOKUP(G330,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="331" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="331" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H331" t="str">
         <f>IF(G331="","",VLOOKUP(G331,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="332" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="332" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H332" t="str">
         <f>IF(G332="","",VLOOKUP(G332,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="333" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="333" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H333" t="str">
         <f>IF(G333="","",VLOOKUP(G333,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="334" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="334" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H334" t="str">
         <f>IF(G334="","",VLOOKUP(G334,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="335" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="335" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H335" t="str">
         <f>IF(G335="","",VLOOKUP(G335,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="336" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="336" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H336" t="str">
         <f>IF(G336="","",VLOOKUP(G336,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="337" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="337" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H337" t="str">
         <f>IF(G337="","",VLOOKUP(G337,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="338" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="338" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H338" t="str">
         <f>IF(G338="","",VLOOKUP(G338,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="339" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="339" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H339" t="str">
         <f>IF(G339="","",VLOOKUP(G339,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="340" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="340" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H340" t="str">
         <f>IF(G340="","",VLOOKUP(G340,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="341" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="341" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H341" t="str">
         <f>IF(G341="","",VLOOKUP(G341,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="342" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="342" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H342" t="str">
         <f>IF(G342="","",VLOOKUP(G342,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="343" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="343" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H343" t="str">
         <f>IF(G343="","",VLOOKUP(G343,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="344" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="344" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H344" t="str">
         <f>IF(G344="","",VLOOKUP(G344,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="345" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="345" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H345" t="str">
         <f>IF(G345="","",VLOOKUP(G345,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="346" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="346" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H346" t="str">
         <f>IF(G346="","",VLOOKUP(G346,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="347" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="347" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H347" t="str">
         <f>IF(G347="","",VLOOKUP(G347,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="348" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="348" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H348" t="str">
         <f>IF(G348="","",VLOOKUP(G348,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="349" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="349" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H349" t="str">
         <f>IF(G349="","",VLOOKUP(G349,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="350" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="350" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H350" t="str">
         <f>IF(G350="","",VLOOKUP(G350,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="351" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="351" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H351" t="str">
         <f>IF(G351="","",VLOOKUP(G351,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="352" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="352" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H352" t="str">
         <f>IF(G352="","",VLOOKUP(G352,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="353" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="353" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H353" t="str">
         <f>IF(G353="","",VLOOKUP(G353,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="354" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="354" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H354" t="str">
         <f>IF(G354="","",VLOOKUP(G354,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="355" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="355" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H355" t="str">
         <f>IF(G355="","",VLOOKUP(G355,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="356" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="356" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H356" t="str">
         <f>IF(G356="","",VLOOKUP(G356,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="357" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="357" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H357" t="str">
         <f>IF(G357="","",VLOOKUP(G357,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="358" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="358" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H358" t="str">
         <f>IF(G358="","",VLOOKUP(G358,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="359" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="359" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H359" t="str">
         <f>IF(G359="","",VLOOKUP(G359,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="360" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="360" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H360" t="str">
         <f>IF(G360="","",VLOOKUP(G360,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="361" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="361" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H361" t="str">
         <f>IF(G361="","",VLOOKUP(G361,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="362" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="362" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H362" t="str">
         <f>IF(G362="","",VLOOKUP(G362,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="363" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="363" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H363" t="str">
         <f>IF(G363="","",VLOOKUP(G363,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="364" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="364" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H364" t="str">
         <f>IF(G364="","",VLOOKUP(G364,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="365" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="365" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H365" t="str">
         <f>IF(G365="","",VLOOKUP(G365,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="366" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="366" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H366" t="str">
         <f>IF(G366="","",VLOOKUP(G366,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="367" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="367" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H367" t="str">
         <f>IF(G367="","",VLOOKUP(G367,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="368" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="368" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H368" t="str">
         <f>IF(G368="","",VLOOKUP(G368,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="369" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="369" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H369" t="str">
         <f>IF(G369="","",VLOOKUP(G369,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="370" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="370" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H370" t="str">
         <f>IF(G370="","",VLOOKUP(G370,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="371" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="371" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H371" t="str">
         <f>IF(G371="","",VLOOKUP(G371,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="372" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="372" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H372" t="str">
         <f>IF(G372="","",VLOOKUP(G372,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="373" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="373" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H373" t="str">
         <f>IF(G373="","",VLOOKUP(G373,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="374" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="374" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H374" t="str">
         <f>IF(G374="","",VLOOKUP(G374,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="375" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="375" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H375" t="str">
         <f>IF(G375="","",VLOOKUP(G375,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="376" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="376" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H376" t="str">
         <f>IF(G376="","",VLOOKUP(G376,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="377" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="377" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H377" t="str">
         <f>IF(G377="","",VLOOKUP(G377,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="378" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="378" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H378" t="str">
         <f>IF(G378="","",VLOOKUP(G378,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="379" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="379" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H379" t="str">
         <f>IF(G379="","",VLOOKUP(G379,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="380" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="380" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H380" t="str">
         <f>IF(G380="","",VLOOKUP(G380,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="381" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="381" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H381" t="str">
         <f>IF(G381="","",VLOOKUP(G381,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="382" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="382" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H382" t="str">
         <f>IF(G382="","",VLOOKUP(G382,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="383" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="383" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H383" t="str">
         <f>IF(G383="","",VLOOKUP(G383,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="384" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="384" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H384" t="str">
         <f>IF(G384="","",VLOOKUP(G384,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="385" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="385" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H385" t="str">
         <f>IF(G385="","",VLOOKUP(G385,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="386" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="386" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H386" t="str">
         <f>IF(G386="","",VLOOKUP(G386,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="387" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="387" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H387" t="str">
         <f>IF(G387="","",VLOOKUP(G387,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="388" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="388" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H388" t="str">
         <f>IF(G388="","",VLOOKUP(G388,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="389" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="389" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H389" t="str">
         <f>IF(G389="","",VLOOKUP(G389,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="390" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="390" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H390" t="str">
         <f>IF(G390="","",VLOOKUP(G390,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="391" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="391" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H391" t="str">
         <f>IF(G391="","",VLOOKUP(G391,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="392" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="392" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H392" t="str">
         <f>IF(G392="","",VLOOKUP(G392,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="393" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="393" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H393" t="str">
         <f>IF(G393="","",VLOOKUP(G393,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="394" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="394" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H394" t="str">
         <f>IF(G394="","",VLOOKUP(G394,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="395" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="395" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H395" t="str">
         <f>IF(G395="","",VLOOKUP(G395,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="396" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="396" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H396" t="str">
         <f>IF(G396="","",VLOOKUP(G396,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="397" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="397" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H397" t="str">
         <f>IF(G397="","",VLOOKUP(G397,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="398" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="398" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H398" t="str">
         <f>IF(G398="","",VLOOKUP(G398,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="399" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="399" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H399" t="str">
         <f>IF(G399="","",VLOOKUP(G399,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="400" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="400" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H400" t="str">
         <f>IF(G400="","",VLOOKUP(G400,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="401" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="401" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H401" t="str">
         <f>IF(G401="","",VLOOKUP(G401,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="402" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="402" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H402" t="str">
         <f>IF(G402="","",VLOOKUP(G402,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="403" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="403" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H403" t="str">
         <f>IF(G403="","",VLOOKUP(G403,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="404" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="404" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H404" t="str">
         <f>IF(G404="","",VLOOKUP(G404,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="405" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="405" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H405" t="str">
         <f>IF(G405="","",VLOOKUP(G405,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="406" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="406" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H406" t="str">
         <f>IF(G406="","",VLOOKUP(G406,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="407" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="407" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H407" t="str">
         <f>IF(G407="","",VLOOKUP(G407,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="408" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="408" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H408" t="str">
         <f>IF(G408="","",VLOOKUP(G408,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="409" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="409" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H409" t="str">
         <f>IF(G409="","",VLOOKUP(G409,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="410" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="410" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H410" t="str">
         <f>IF(G410="","",VLOOKUP(G410,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="411" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="411" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H411" t="str">
         <f>IF(G411="","",VLOOKUP(G411,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="412" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="412" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H412" t="str">
         <f>IF(G412="","",VLOOKUP(G412,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="413" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="413" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H413" t="str">
         <f>IF(G413="","",VLOOKUP(G413,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="414" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="414" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H414" t="str">
         <f>IF(G414="","",VLOOKUP(G414,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="415" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="415" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H415" t="str">
         <f>IF(G415="","",VLOOKUP(G415,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="416" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="416" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H416" t="str">
         <f>IF(G416="","",VLOOKUP(G416,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="417" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="417" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H417" t="str">
         <f>IF(G417="","",VLOOKUP(G417,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="418" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="418" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H418" t="str">
         <f>IF(G418="","",VLOOKUP(G418,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="419" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="419" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H419" t="str">
         <f>IF(G419="","",VLOOKUP(G419,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="420" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="420" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H420" t="str">
         <f>IF(G420="","",VLOOKUP(G420,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="421" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="421" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H421" t="str">
         <f>IF(G421="","",VLOOKUP(G421,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="422" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="422" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H422" t="str">
         <f>IF(G422="","",VLOOKUP(G422,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="423" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="423" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H423" t="str">
         <f>IF(G423="","",VLOOKUP(G423,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="424" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="424" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H424" t="str">
         <f>IF(G424="","",VLOOKUP(G424,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="425" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="425" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H425" t="str">
         <f>IF(G425="","",VLOOKUP(G425,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="426" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="426" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H426" t="str">
         <f>IF(G426="","",VLOOKUP(G426,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="427" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="427" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H427" t="str">
         <f>IF(G427="","",VLOOKUP(G427,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="428" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="428" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H428" t="str">
         <f>IF(G428="","",VLOOKUP(G428,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="429" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="429" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H429" t="str">
         <f>IF(G429="","",VLOOKUP(G429,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="430" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="430" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H430" t="str">
         <f>IF(G430="","",VLOOKUP(G430,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="431" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="431" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H431" t="str">
         <f>IF(G431="","",VLOOKUP(G431,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="432" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="432" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H432" t="str">
         <f>IF(G432="","",VLOOKUP(G432,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="433" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="433" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H433" t="str">
         <f>IF(G433="","",VLOOKUP(G433,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="434" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="434" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H434" t="str">
         <f>IF(G434="","",VLOOKUP(G434,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="435" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="435" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H435" t="str">
         <f>IF(G435="","",VLOOKUP(G435,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="436" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="436" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H436" t="str">
         <f>IF(G436="","",VLOOKUP(G436,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="437" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="437" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H437" t="str">
         <f>IF(G437="","",VLOOKUP(G437,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="438" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="438" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H438" t="str">
         <f>IF(G438="","",VLOOKUP(G438,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="439" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="439" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H439" t="str">
         <f>IF(G439="","",VLOOKUP(G439,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="440" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="440" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H440" t="str">
         <f>IF(G440="","",VLOOKUP(G440,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="441" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="441" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H441" t="str">
         <f>IF(G441="","",VLOOKUP(G441,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="442" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="442" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H442" t="str">
         <f>IF(G442="","",VLOOKUP(G442,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="443" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="443" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H443" t="str">
         <f>IF(G443="","",VLOOKUP(G443,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="444" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="444" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H444" t="str">
         <f>IF(G444="","",VLOOKUP(G444,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="445" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="445" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H445" t="str">
         <f>IF(G445="","",VLOOKUP(G445,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="446" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="446" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H446" t="str">
         <f>IF(G446="","",VLOOKUP(G446,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="447" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="447" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H447" t="str">
         <f>IF(G447="","",VLOOKUP(G447,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="448" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="448" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H448" t="str">
         <f>IF(G448="","",VLOOKUP(G448,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="449" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="449" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H449" t="str">
         <f>IF(G449="","",VLOOKUP(G449,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="450" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="450" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H450" t="str">
         <f>IF(G450="","",VLOOKUP(G450,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="451" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="451" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H451" t="str">
         <f>IF(G451="","",VLOOKUP(G451,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="452" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="452" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H452" t="str">
         <f>IF(G452="","",VLOOKUP(G452,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="453" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="453" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H453" t="str">
         <f>IF(G453="","",VLOOKUP(G453,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="454" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="454" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H454" t="str">
         <f>IF(G454="","",VLOOKUP(G454,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="455" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="455" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H455" t="str">
         <f>IF(G455="","",VLOOKUP(G455,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="456" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="456" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H456" t="str">
         <f>IF(G456="","",VLOOKUP(G456,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="457" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="457" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H457" t="str">
         <f>IF(G457="","",VLOOKUP(G457,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="458" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="458" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H458" t="str">
         <f>IF(G458="","",VLOOKUP(G458,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="459" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="459" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H459" t="str">
         <f>IF(G459="","",VLOOKUP(G459,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="460" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="460" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H460" t="str">
         <f>IF(G460="","",VLOOKUP(G460,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="461" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="461" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H461" t="str">
         <f>IF(G461="","",VLOOKUP(G461,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="462" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="462" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H462" t="str">
         <f>IF(G462="","",VLOOKUP(G462,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="463" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="463" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H463" t="str">
         <f>IF(G463="","",VLOOKUP(G463,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="464" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="464" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H464" t="str">
         <f>IF(G464="","",VLOOKUP(G464,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="465" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="465" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H465" t="str">
         <f>IF(G465="","",VLOOKUP(G465,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="466" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="466" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H466" t="str">
         <f>IF(G466="","",VLOOKUP(G466,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="467" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="467" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H467" t="str">
         <f>IF(G467="","",VLOOKUP(G467,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="468" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="468" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H468" t="str">
         <f>IF(G468="","",VLOOKUP(G468,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="469" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="469" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H469" t="str">
         <f>IF(G469="","",VLOOKUP(G469,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="470" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="470" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H470" t="str">
         <f>IF(G470="","",VLOOKUP(G470,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="471" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="471" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H471" t="str">
         <f>IF(G471="","",VLOOKUP(G471,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="472" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="472" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H472" t="str">
         <f>IF(G472="","",VLOOKUP(G472,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="473" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="473" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H473" t="str">
         <f>IF(G473="","",VLOOKUP(G473,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="474" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="474" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H474" t="str">
         <f>IF(G474="","",VLOOKUP(G474,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="475" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="475" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H475" t="str">
         <f>IF(G475="","",VLOOKUP(G475,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="476" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="476" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H476" t="str">
         <f>IF(G476="","",VLOOKUP(G476,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="477" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="477" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H477" t="str">
         <f>IF(G477="","",VLOOKUP(G477,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="478" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="478" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H478" t="str">
         <f>IF(G478="","",VLOOKUP(G478,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="479" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="479" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H479" t="str">
         <f>IF(G479="","",VLOOKUP(G479,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="480" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="480" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H480" t="str">
         <f>IF(G480="","",VLOOKUP(G480,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="481" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="481" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H481" t="str">
         <f>IF(G481="","",VLOOKUP(G481,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="482" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="482" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H482" t="str">
         <f>IF(G482="","",VLOOKUP(G482,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="483" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="483" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H483" t="str">
         <f>IF(G483="","",VLOOKUP(G483,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="484" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="484" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H484" t="str">
         <f>IF(G484="","",VLOOKUP(G484,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="485" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="485" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H485" t="str">
         <f>IF(G485="","",VLOOKUP(G485,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="486" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="486" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H486" t="str">
         <f>IF(G486="","",VLOOKUP(G486,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="487" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="487" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H487" t="str">
         <f>IF(G487="","",VLOOKUP(G487,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="488" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="488" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H488" t="str">
         <f>IF(G488="","",VLOOKUP(G488,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="489" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="489" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H489" t="str">
         <f>IF(G489="","",VLOOKUP(G489,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="490" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="490" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H490" t="str">
         <f>IF(G490="","",VLOOKUP(G490,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="491" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="491" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H491" t="str">
         <f>IF(G491="","",VLOOKUP(G491,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="492" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="492" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H492" t="str">
         <f>IF(G492="","",VLOOKUP(G492,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="493" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="493" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H493" t="str">
         <f>IF(G493="","",VLOOKUP(G493,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="494" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="494" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H494" t="str">
         <f>IF(G494="","",VLOOKUP(G494,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="495" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="495" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H495" t="str">
         <f>IF(G495="","",VLOOKUP(G495,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="496" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="496" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H496" t="str">
         <f>IF(G496="","",VLOOKUP(G496,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="497" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="497" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H497" t="str">
         <f>IF(G497="","",VLOOKUP(G497,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="498" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="498" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H498" t="str">
         <f>IF(G498="","",VLOOKUP(G498,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="499" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="499" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H499" t="str">
         <f>IF(G499="","",VLOOKUP(G499,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="500" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="500" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H500" t="str">
         <f>IF(G500="","",VLOOKUP(G500,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
@@ -26915,15 +26922,15 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1">
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>REFERENCIA!$A$1:$A$15</xm:f>
           </x14:formula1>
           <xm:sqref>G35:G500</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1">
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
-            <xm:f>[1]REFERENCIA!#REF!</xm:f>
+            <xm:f>'C:\Users\MONITOR7\Desktop\[Abril_Santa_Rita_Mora.xlsx]REFERENCIA'!#REF!</xm:f>
           </x14:formula1>
           <xm:sqref>G2:G34 I2:I30</xm:sqref>
         </x14:dataValidation>
@@ -26934,11 +26941,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.9375" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.921875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -26946,7 +26953,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -26954,7 +26961,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -26962,7 +26969,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -26970,7 +26977,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -26978,7 +26985,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -26986,7 +26993,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -26994,7 +27001,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -27002,7 +27009,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -27010,7 +27017,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -27018,7 +27025,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -27026,7 +27033,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -27034,7 +27041,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -27042,7 +27049,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -27050,7 +27057,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>30</v>
       </c>
